--- a/NATIONDRIVE_Road_Accidents_2016_2026.xlsx
+++ b/NATIONDRIVE_Road_Accidents_2016_2026.xlsx
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -71,6 +71,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,10 +505,10 @@
       <c r="D2" s="4" t="n">
         <v>8541</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="6" t="n">
         <v>34.31774349083896</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="6" t="n">
         <v>65.68225650916105</v>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -529,10 +532,10 @@
       <c r="D3" s="4" t="n">
         <v>8060</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="6" t="n">
         <v>31.32895401718039</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="6" t="n">
         <v>68.67104598281961</v>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -556,10 +559,10 @@
       <c r="D4" s="4" t="n">
         <v>7556</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="6" t="n">
         <v>30.87231869254341</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="6" t="n">
         <v>69.12768130745658</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -583,10 +586,10 @@
       <c r="D5" s="4" t="n">
         <v>7984</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>36.30411058566752</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="6" t="n">
         <v>63.69588941433248</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -610,10 +613,10 @@
       <c r="D6" s="4" t="n">
         <v>7039</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="6" t="n">
         <v>36.08078322825363</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="6" t="n">
         <v>63.91921677174637</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -637,10 +640,10 @@
       <c r="D7" s="4" t="n">
         <v>8186</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="6" t="n">
         <v>37.97550565967713</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="6" t="n">
         <v>62.02449434032287</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -664,10 +667,10 @@
       <c r="D8" s="4" t="n">
         <v>8293</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="6" t="n">
         <v>39.02771895148007</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="6" t="n">
         <v>60.97228104851993</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -691,10 +694,10 @@
       <c r="D9" s="4" t="n">
         <v>8137</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="6" t="n">
         <v>40.78901198055041</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="6" t="n">
         <v>59.21098801944959</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -718,10 +721,10 @@
       <c r="D10" s="4" t="n">
         <v>8346</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="6" t="n">
         <v>42.67525694124866</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="6" t="n">
         <v>57.32474305875134</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -739,13 +742,21 @@
       <c r="B11" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="C11" s="4" t="n">
+        <v>11834</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>8326</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>70.35659962818997</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>29.64340037181003</v>
+      </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -758,13 +769,21 @@
       <c r="B12" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="C12" s="4" t="n">
+        <v>9910</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>4510</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>45.50958627648839</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>54.49041372351161</v>
+      </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -783,10 +802,10 @@
       <c r="D13" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="6" t="n">
         <v>59.83935742971887</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="6" t="n">
         <v>40.16064257028113</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -810,10 +829,10 @@
       <c r="D14" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="6" t="n">
         <v>45.64315352697096</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="6" t="n">
         <v>54.35684647302904</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -837,10 +856,10 @@
       <c r="D15" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="6" t="n">
         <v>63.1768953068592</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="6" t="n">
         <v>36.8231046931408</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -864,10 +883,10 @@
       <c r="D16" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="6" t="n">
         <v>53.58649789029536</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="6" t="n">
         <v>46.41350210970464</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -891,10 +910,10 @@
       <c r="D17" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="6" t="n">
         <v>54.47761194029851</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="6" t="n">
         <v>45.52238805970149</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -918,10 +937,10 @@
       <c r="D18" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="6" t="n">
         <v>55.47703180212014</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="6" t="n">
         <v>44.52296819787986</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -945,10 +964,10 @@
       <c r="D19" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="6" t="n">
         <v>65.19823788546255</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="6" t="n">
         <v>34.80176211453745</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -972,10 +991,10 @@
       <c r="D20" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="6" t="n">
         <v>50.52264808362369</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="6" t="n">
         <v>49.47735191637631</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -999,10 +1018,10 @@
       <c r="D21" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="6" t="n">
         <v>60.64981949458483</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="6" t="n">
         <v>39.35018050541517</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1020,13 +1039,21 @@
       <c r="B22" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="C22" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>81.73076923076923</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>18.26923076923077</v>
+      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1066,21 @@
       <c r="B23" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="C23" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>60.3448275862069</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>39.6551724137931</v>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -1064,10 +1099,10 @@
       <c r="D24" s="4" t="n">
         <v>2572</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="6" t="n">
         <v>34.59314055144587</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="6" t="n">
         <v>65.40685944855413</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1091,10 +1126,10 @@
       <c r="D25" s="4" t="n">
         <v>2783</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="6" t="n">
         <v>38.81450488145049</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="6" t="n">
         <v>61.18549511854951</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1118,10 +1153,10 @@
       <c r="D26" s="4" t="n">
         <v>2966</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="6" t="n">
         <v>35.96023278370514</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="6" t="n">
         <v>64.03976721629485</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1145,10 +1180,10 @@
       <c r="D27" s="4" t="n">
         <v>3208</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="6" t="n">
         <v>38.41916167664671</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="6" t="n">
         <v>61.58083832335329</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1172,10 +1207,10 @@
       <c r="D28" s="4" t="n">
         <v>2629</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="6" t="n">
         <v>39.86353297952995</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="6" t="n">
         <v>60.13646702047005</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -1199,10 +1234,10 @@
       <c r="D29" s="4" t="n">
         <v>3036</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="6" t="n">
         <v>40.96613142625826</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="6" t="n">
         <v>59.03386857374174</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1226,10 +1261,10 @@
       <c r="D30" s="4" t="n">
         <v>2994</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="6" t="n">
         <v>42.63135412217001</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="6" t="n">
         <v>57.36864587782999</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1253,10 +1288,10 @@
       <c r="D31" s="4" t="n">
         <v>3296</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="6" t="n">
         <v>44.41449939361272</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="6" t="n">
         <v>55.58550060638728</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -1280,10 +1315,10 @@
       <c r="D32" s="4" t="n">
         <v>3351</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="6" t="n">
         <v>42.69877675840979</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="6" t="n">
         <v>57.30122324159021</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -1301,13 +1336,21 @@
       <c r="B33" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
+      <c r="C33" s="4" t="n">
+        <v>16026</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>3907</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>24.37913390740047</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>75.62086609259953</v>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -1320,13 +1363,21 @@
       <c r="B34" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
+      <c r="C34" s="4" t="n">
+        <v>9758</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>2198</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>22.52510760401722</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>77.47489239598278</v>
+      </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -1345,10 +1396,10 @@
       <c r="D35" s="4" t="n">
         <v>4901</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="6" t="n">
         <v>59.60836779372416</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="6" t="n">
         <v>40.39163220627584</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -1372,10 +1423,10 @@
       <c r="D36" s="4" t="n">
         <v>5554</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="6" t="n">
         <v>62.72162619988707</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="6" t="n">
         <v>37.27837380011293</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -1399,10 +1450,10 @@
       <c r="D37" s="4" t="n">
         <v>6729</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="6" t="n">
         <v>70.09375</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="6" t="n">
         <v>29.90625</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -1426,10 +1477,10 @@
       <c r="D38" s="4" t="n">
         <v>7205</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="6" t="n">
         <v>71.99960027980413</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="6" t="n">
         <v>28.00039972019587</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -1453,10 +1504,10 @@
       <c r="D39" s="4" t="n">
         <v>6699</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="6" t="n">
         <v>77.54369718717444</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="6" t="n">
         <v>22.45630281282556</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -1480,10 +1531,10 @@
       <c r="D40" s="4" t="n">
         <v>7660</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="6" t="n">
         <v>80.18423531874804</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="6" t="n">
         <v>19.81576468125196</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -1507,10 +1558,10 @@
       <c r="D41" s="4" t="n">
         <v>8898</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="6" t="n">
         <v>82.38126099435237</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="6" t="n">
         <v>17.61873900564763</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -1534,10 +1585,10 @@
       <c r="D42" s="4" t="n">
         <v>8873</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="6" t="n">
         <v>80.56110404939169</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="6" t="n">
         <v>19.43889595060831</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -1561,10 +1612,10 @@
       <c r="D43" s="4" t="n">
         <v>9347</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="6" t="n">
         <v>80.50818260120586</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="6" t="n">
         <v>19.49181739879414</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -1582,13 +1633,21 @@
       <c r="B44" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="C44" s="4" t="n">
+        <v>12610</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>10394</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>82.42664551942902</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>17.57335448057098</v>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -1601,13 +1660,21 @@
       <c r="B45" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
+      <c r="C45" s="4" t="n">
+        <v>7440</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>6249</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>83.99193548387098</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>16.00806451612902</v>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -1626,10 +1693,10 @@
       <c r="D46" s="4" t="n">
         <v>3908</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E46" s="6" t="n">
         <v>28.77761413843888</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="6" t="n">
         <v>71.22238586156112</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -1653,10 +1720,10 @@
       <c r="D47" s="4" t="n">
         <v>4136</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E47" s="6" t="n">
         <v>30.49472830494728</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="6" t="n">
         <v>69.50527169505271</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -1680,10 +1747,10 @@
       <c r="D48" s="4" t="n">
         <v>4592</v>
       </c>
-      <c r="E48" s="4" t="n">
+      <c r="E48" s="6" t="n">
         <v>33.12175418349683</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="6" t="n">
         <v>66.87824581650318</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -1707,10 +1774,10 @@
       <c r="D49" s="4" t="n">
         <v>5003</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E49" s="6" t="n">
         <v>35.99539535218361</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="6" t="n">
         <v>64.00460464781639</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -1734,10 +1801,10 @@
       <c r="D50" s="4" t="n">
         <v>4606</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="E50" s="6" t="n">
         <v>39.51612903225806</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="6" t="n">
         <v>60.48387096774194</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -1761,10 +1828,10 @@
       <c r="D51" s="4" t="n">
         <v>5371</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="E51" s="6" t="n">
         <v>43.4020202020202</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="6" t="n">
         <v>56.5979797979798</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -1788,10 +1855,10 @@
       <c r="D52" s="4" t="n">
         <v>5834</v>
       </c>
-      <c r="E52" s="4" t="n">
+      <c r="E52" s="6" t="n">
         <v>43.93403117704646</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="6" t="n">
         <v>56.06596882295354</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -1815,10 +1882,10 @@
       <c r="D53" s="4" t="n">
         <v>6166</v>
       </c>
-      <c r="E53" s="4" t="n">
+      <c r="E53" s="6" t="n">
         <v>45.78259578259578</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="6" t="n">
         <v>54.21740421740422</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -1842,10 +1909,10 @@
       <c r="D54" s="4" t="n">
         <v>6945</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="6" t="n">
         <v>46.74564178501716</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="F54" s="6" t="n">
         <v>53.25435821498284</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -1863,13 +1930,21 @@
       <c r="B55" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
+      <c r="C55" s="4" t="n">
+        <v>13598</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>6941</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>51.04427121635534</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>48.95572878364466</v>
+      </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1957,21 @@
       <c r="B56" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
+      <c r="C56" s="4" t="n">
+        <v>6110</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>2833</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>46.36661211129296</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>53.63338788870704</v>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -1907,10 +1990,10 @@
       <c r="D57" s="4" t="n">
         <v>336</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="6" t="n">
         <v>7.806691449814126</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="6" t="n">
         <v>92.19330855018588</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -1934,10 +2017,10 @@
       <c r="D58" s="4" t="n">
         <v>328</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="6" t="n">
         <v>8.373755425070206</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="6" t="n">
         <v>91.6262445749298</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -1961,10 +2044,10 @@
       <c r="D59" s="4" t="n">
         <v>262</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="6" t="n">
         <v>7.063898624966298</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="6" t="n">
         <v>92.9361013750337</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -1988,10 +2071,10 @@
       <c r="D60" s="4" t="n">
         <v>297</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="6" t="n">
         <v>8.633720930232558</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="F60" s="6" t="n">
         <v>91.36627906976744</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -2015,10 +2098,10 @@
       <c r="D61" s="4" t="n">
         <v>223</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="6" t="n">
         <v>9.389473684210527</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="F61" s="6" t="n">
         <v>90.61052631578947</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -2042,10 +2125,10 @@
       <c r="D62" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="E62" s="6" t="n">
         <v>7.932607932607932</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="F62" s="6" t="n">
         <v>92.06739206739206</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -2069,10 +2152,10 @@
       <c r="D63" s="4" t="n">
         <v>271</v>
       </c>
-      <c r="E63" s="4" t="n">
+      <c r="E63" s="6" t="n">
         <v>9.000332115576221</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="F63" s="6" t="n">
         <v>90.99966788442379</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -2096,10 +2179,10 @@
       <c r="D64" s="4" t="n">
         <v>290</v>
       </c>
-      <c r="E64" s="4" t="n">
+      <c r="E64" s="6" t="n">
         <v>10.18973998594519</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="6" t="n">
         <v>89.81026001405482</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -2123,10 +2206,10 @@
       <c r="D65" s="4" t="n">
         <v>286</v>
       </c>
-      <c r="E65" s="4" t="n">
+      <c r="E65" s="6" t="n">
         <v>10.66368381804623</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="F65" s="6" t="n">
         <v>89.33631618195376</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -2144,13 +2227,21 @@
       <c r="B66" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="4" t="n"/>
+      <c r="C66" s="4" t="n">
+        <v>2375</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>11.49473684210526</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>88.50526315789473</v>
+      </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -2163,13 +2254,21 @@
       <c r="B67" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="4" t="n"/>
+      <c r="C67" s="4" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>10.07437457741717</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>89.92562542258283</v>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -2188,10 +2287,10 @@
       <c r="D68" s="4" t="n">
         <v>8136</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="6" t="n">
         <v>37.22036689693032</v>
       </c>
-      <c r="F68" s="4" t="n">
+      <c r="F68" s="6" t="n">
         <v>62.77963310306968</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -2215,10 +2314,10 @@
       <c r="D69" s="4" t="n">
         <v>7289</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="6" t="n">
         <v>38.20030396729731</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="6" t="n">
         <v>61.79969603270269</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -2242,10 +2341,10 @@
       <c r="D70" s="4" t="n">
         <v>7996</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="6" t="n">
         <v>42.6021631413501</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="F70" s="6" t="n">
         <v>57.3978368586499</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -2269,10 +2368,10 @@
       <c r="D71" s="4" t="n">
         <v>7390</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="6" t="n">
         <v>43.35327936172709</v>
       </c>
-      <c r="F71" s="4" t="n">
+      <c r="F71" s="6" t="n">
         <v>56.64672063827291</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -2296,10 +2395,10 @@
       <c r="D72" s="4" t="n">
         <v>6170</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="6" t="n">
         <v>46.05164949992536</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="6" t="n">
         <v>53.94835050007464</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -2323,10 +2422,10 @@
       <c r="D73" s="4" t="n">
         <v>7452</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="6" t="n">
         <v>49.07151323587514</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="F73" s="6" t="n">
         <v>50.92848676412486</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -2350,10 +2449,10 @@
       <c r="D74" s="4" t="n">
         <v>7618</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E74" s="6" t="n">
         <v>48.36518316297378</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="6" t="n">
         <v>51.63481683702622</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -2377,10 +2476,10 @@
       <c r="D75" s="4" t="n">
         <v>7854</v>
       </c>
-      <c r="E75" s="4" t="n">
+      <c r="E75" s="6" t="n">
         <v>48.03963545170959</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="6" t="n">
         <v>51.96036454829041</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -2404,10 +2503,10 @@
       <c r="D76" s="4" t="n">
         <v>7717</v>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E76" s="6" t="n">
         <v>49.50603027970234</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="F76" s="6" t="n">
         <v>50.49396972029766</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -2425,13 +2524,21 @@
       <c r="B77" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
+      <c r="C77" s="4" t="n">
+        <v>18292</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>8402</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>45.93264815219768</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>54.06735184780232</v>
+      </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -2444,13 +2551,21 @@
       <c r="B78" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="n"/>
+      <c r="C78" s="4" t="n">
+        <v>16112</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>4763</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>29.56181727904668</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>70.43818272095332</v>
+      </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -2469,10 +2584,10 @@
       <c r="D79" s="4" t="n">
         <v>5024</v>
       </c>
-      <c r="E79" s="4" t="n">
+      <c r="E79" s="6" t="n">
         <v>44.72138152038455</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="6" t="n">
         <v>55.27861847961545</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -2496,10 +2611,10 @@
       <c r="D80" s="4" t="n">
         <v>5120</v>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E80" s="6" t="n">
         <v>45.47877065198082</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="F80" s="6" t="n">
         <v>54.52122934801918</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -2523,10 +2638,10 @@
       <c r="D81" s="4" t="n">
         <v>5118</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="E81" s="6" t="n">
         <v>45.54191137213027</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="F81" s="6" t="n">
         <v>54.45808862786973</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -2550,10 +2665,10 @@
       <c r="D82" s="4" t="n">
         <v>5057</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="E82" s="6" t="n">
         <v>46.20796783625731</v>
       </c>
-      <c r="F82" s="4" t="n">
+      <c r="F82" s="6" t="n">
         <v>53.79203216374269</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -2577,10 +2692,10 @@
       <c r="D83" s="4" t="n">
         <v>4507</v>
       </c>
-      <c r="E83" s="4" t="n">
+      <c r="E83" s="6" t="n">
         <v>47.78920581062454</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="6" t="n">
         <v>52.21079418937546</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -2604,10 +2719,10 @@
       <c r="D84" s="4" t="n">
         <v>4706</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="E84" s="6" t="n">
         <v>47.37742877277761</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="6" t="n">
         <v>52.62257122722239</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -2631,10 +2746,10 @@
       <c r="D85" s="4" t="n">
         <v>4915</v>
       </c>
-      <c r="E85" s="4" t="n">
+      <c r="E85" s="6" t="n">
         <v>47.12820021095023</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F85" s="6" t="n">
         <v>52.87179978904977</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -2658,10 +2773,10 @@
       <c r="D86" s="4" t="n">
         <v>4968</v>
       </c>
-      <c r="E86" s="4" t="n">
+      <c r="E86" s="6" t="n">
         <v>47.48160183503775</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="6" t="n">
         <v>52.51839816496225</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -2685,10 +2800,10 @@
       <c r="D87" s="4" t="n">
         <v>4689</v>
       </c>
-      <c r="E87" s="4" t="n">
+      <c r="E87" s="6" t="n">
         <v>47.81766265551703</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="6" t="n">
         <v>52.18233734448297</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -2706,13 +2821,21 @@
       <c r="B88" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C88" s="4" t="n"/>
-      <c r="D88" s="4" t="n"/>
-      <c r="E88" s="4" t="n"/>
-      <c r="F88" s="4" t="n"/>
+      <c r="C88" s="4" t="n">
+        <v>15139</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>5168</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>34.13699715965387</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>65.86300284034613</v>
+      </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -2725,13 +2848,21 @@
       <c r="B89" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
+      <c r="C89" s="4" t="n">
+        <v>8302</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>3022</v>
+      </c>
+      <c r="E89" s="6" t="n">
+        <v>36.40086726090099</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>63.59913273909901</v>
+      </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -2750,10 +2881,10 @@
       <c r="D90" s="4" t="n">
         <v>1271</v>
       </c>
-      <c r="E90" s="4" t="n">
+      <c r="E90" s="6" t="n">
         <v>40.11994949494949</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="F90" s="6" t="n">
         <v>59.88005050505051</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
@@ -2777,10 +2908,10 @@
       <c r="D91" s="4" t="n">
         <v>1203</v>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E91" s="6" t="n">
         <v>38.63198458574181</v>
       </c>
-      <c r="F91" s="4" t="n">
+      <c r="F91" s="6" t="n">
         <v>61.36801541425819</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -2804,10 +2935,10 @@
       <c r="D92" s="4" t="n">
         <v>1208</v>
       </c>
-      <c r="E92" s="4" t="n">
+      <c r="E92" s="6" t="n">
         <v>38.84244372990354</v>
       </c>
-      <c r="F92" s="4" t="n">
+      <c r="F92" s="6" t="n">
         <v>61.15755627009646</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -2831,10 +2962,10 @@
       <c r="D93" s="4" t="n">
         <v>1146</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="E93" s="6" t="n">
         <v>39.88861816916116</v>
       </c>
-      <c r="F93" s="4" t="n">
+      <c r="F93" s="6" t="n">
         <v>60.11138183083884</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
@@ -2858,10 +2989,10 @@
       <c r="D94" s="4" t="n">
         <v>893</v>
       </c>
-      <c r="E94" s="4" t="n">
+      <c r="E94" s="6" t="n">
         <v>39.88387673068334</v>
       </c>
-      <c r="F94" s="4" t="n">
+      <c r="F94" s="6" t="n">
         <v>60.11612326931666</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -2885,10 +3016,10 @@
       <c r="D95" s="4" t="n">
         <v>1052</v>
       </c>
-      <c r="E95" s="4" t="n">
+      <c r="E95" s="6" t="n">
         <v>43.7603993344426</v>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="6" t="n">
         <v>56.2396006655574</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -2912,10 +3043,10 @@
       <c r="D96" s="4" t="n">
         <v>1032</v>
       </c>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="6" t="n">
         <v>39.73815941470928</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="6" t="n">
         <v>60.26184058529072</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -2939,10 +3070,10 @@
       <c r="D97" s="4" t="n">
         <v>889</v>
       </c>
-      <c r="E97" s="4" t="n">
+      <c r="E97" s="6" t="n">
         <v>39.45849977807368</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F97" s="6" t="n">
         <v>60.54150022192632</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -2966,10 +3097,10 @@
       <c r="D98" s="4" t="n">
         <v>869</v>
       </c>
-      <c r="E98" s="4" t="n">
+      <c r="E98" s="6" t="n">
         <v>40.30612244897959</v>
       </c>
-      <c r="F98" s="4" t="n">
+      <c r="F98" s="6" t="n">
         <v>59.69387755102041</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
@@ -2987,13 +3118,21 @@
       <c r="B99" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C99" s="4" t="n"/>
-      <c r="D99" s="4" t="n"/>
-      <c r="E99" s="4" t="n"/>
-      <c r="F99" s="4" t="n"/>
+      <c r="C99" s="4" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>802</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>41.57594608605495</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>58.42405391394505</v>
+      </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -3006,13 +3145,21 @@
       <c r="B100" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n"/>
-      <c r="F100" s="4" t="n"/>
+      <c r="C100" s="4" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>565</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>39.90112994350282</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>60.09887005649718</v>
+      </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -3031,10 +3178,10 @@
       <c r="D101" s="4" t="n">
         <v>3027</v>
       </c>
-      <c r="E101" s="4" t="n">
+      <c r="E101" s="6" t="n">
         <v>61.37469586374696</v>
       </c>
-      <c r="F101" s="4" t="n">
+      <c r="F101" s="6" t="n">
         <v>38.62530413625304</v>
       </c>
       <c r="G101" s="4" t="inlineStr">
@@ -3058,10 +3205,10 @@
       <c r="D102" s="4" t="n">
         <v>3256</v>
       </c>
-      <c r="E102" s="4" t="n">
+      <c r="E102" s="6" t="n">
         <v>62.63947672181608</v>
       </c>
-      <c r="F102" s="4" t="n">
+      <c r="F102" s="6" t="n">
         <v>37.36052327818392</v>
       </c>
       <c r="G102" s="4" t="inlineStr">
@@ -3085,10 +3232,10 @@
       <c r="D103" s="4" t="n">
         <v>3542</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="E103" s="6" t="n">
         <v>65.66555431961439</v>
       </c>
-      <c r="F103" s="4" t="n">
+      <c r="F103" s="6" t="n">
         <v>34.33444568038561</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -3112,10 +3259,10 @@
       <c r="D104" s="4" t="n">
         <v>3801</v>
       </c>
-      <c r="E104" s="4" t="n">
+      <c r="E104" s="6" t="n">
         <v>72.85796434732606</v>
       </c>
-      <c r="F104" s="4" t="n">
+      <c r="F104" s="6" t="n">
         <v>27.14203565267394</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -3139,10 +3286,10 @@
       <c r="D105" s="4" t="n">
         <v>3044</v>
       </c>
-      <c r="E105" s="4" t="n">
+      <c r="E105" s="6" t="n">
         <v>69.10329171396141</v>
       </c>
-      <c r="F105" s="4" t="n">
+      <c r="F105" s="6" t="n">
         <v>30.89670828603859</v>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -3166,10 +3313,10 @@
       <c r="D106" s="4" t="n">
         <v>3513</v>
       </c>
-      <c r="E106" s="4" t="n">
+      <c r="E106" s="6" t="n">
         <v>74.30203045685279</v>
       </c>
-      <c r="F106" s="4" t="n">
+      <c r="F106" s="6" t="n">
         <v>25.69796954314721</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -3193,10 +3340,10 @@
       <c r="D107" s="4" t="n">
         <v>3898</v>
       </c>
-      <c r="E107" s="4" t="n">
+      <c r="E107" s="6" t="n">
         <v>75.32367149758454</v>
       </c>
-      <c r="F107" s="4" t="n">
+      <c r="F107" s="6" t="n">
         <v>24.67632850241546</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -3220,10 +3367,10 @@
       <c r="D108" s="4" t="n">
         <v>4173</v>
       </c>
-      <c r="E108" s="4" t="n">
+      <c r="E108" s="6" t="n">
         <v>78.51364063969896</v>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F108" s="6" t="n">
         <v>21.48635936030104</v>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -3247,10 +3394,10 @@
       <c r="D109" s="4" t="n">
         <v>4114</v>
       </c>
-      <c r="E109" s="4" t="n">
+      <c r="E109" s="6" t="n">
         <v>79.17628945342571</v>
       </c>
-      <c r="F109" s="4" t="n">
+      <c r="F109" s="6" t="n">
         <v>20.82371054657429</v>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -3268,13 +3415,21 @@
       <c r="B110" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="4" t="n"/>
+      <c r="C110" s="4" t="n">
+        <v>5969</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>4821</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>80.76729770480817</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>19.23270229519183</v>
+      </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3442,21 @@
       <c r="B111" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="4" t="n"/>
-      <c r="F111" s="4" t="n"/>
+      <c r="C111" s="4" t="n">
+        <v>3210</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>2581</v>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>80.40498442367601</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>19.59501557632399</v>
+      </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -3312,10 +3475,10 @@
       <c r="D112" s="4" t="n">
         <v>11133</v>
       </c>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="6" t="n">
         <v>25.07263022768732</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="6" t="n">
         <v>74.92736977231269</v>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -3339,10 +3502,10 @@
       <c r="D113" s="4" t="n">
         <v>10609</v>
       </c>
-      <c r="E113" s="4" t="n">
+      <c r="E113" s="6" t="n">
         <v>24.93770861736636</v>
       </c>
-      <c r="F113" s="4" t="n">
+      <c r="F113" s="6" t="n">
         <v>75.06229138263363</v>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -3366,10 +3529,10 @@
       <c r="D114" s="4" t="n">
         <v>10990</v>
       </c>
-      <c r="E114" s="4" t="n">
+      <c r="E114" s="6" t="n">
         <v>26.35049272304409</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="6" t="n">
         <v>73.6495072769559</v>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -3393,10 +3556,10 @@
       <c r="D115" s="4" t="n">
         <v>10958</v>
       </c>
-      <c r="E115" s="4" t="n">
+      <c r="E115" s="6" t="n">
         <v>26.95164543263319</v>
       </c>
-      <c r="F115" s="4" t="n">
+      <c r="F115" s="6" t="n">
         <v>73.04835456736681</v>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -3420,10 +3583,10 @@
       <c r="D116" s="4" t="n">
         <v>9760</v>
       </c>
-      <c r="E116" s="4" t="n">
+      <c r="E116" s="6" t="n">
         <v>28.55638129791094</v>
       </c>
-      <c r="F116" s="4" t="n">
+      <c r="F116" s="6" t="n">
         <v>71.44361870208905</v>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -3447,10 +3610,10 @@
       <c r="D117" s="4" t="n">
         <v>10038</v>
       </c>
-      <c r="E117" s="4" t="n">
+      <c r="E117" s="6" t="n">
         <v>28.97220538574769</v>
       </c>
-      <c r="F117" s="4" t="n">
+      <c r="F117" s="6" t="n">
         <v>71.02779461425231</v>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -3474,10 +3637,10 @@
       <c r="D118" s="4" t="n">
         <v>11702</v>
       </c>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="6" t="n">
         <v>29.43010914943916</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="6" t="n">
         <v>70.56989085056084</v>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -3501,10 +3664,10 @@
       <c r="D119" s="4" t="n">
         <v>12321</v>
       </c>
-      <c r="E119" s="4" t="n">
+      <c r="E119" s="6" t="n">
         <v>28.36325966850829</v>
       </c>
-      <c r="F119" s="4" t="n">
+      <c r="F119" s="6" t="n">
         <v>71.63674033149171</v>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -3528,10 +3691,10 @@
       <c r="D120" s="4" t="n">
         <v>12390</v>
       </c>
-      <c r="E120" s="4" t="n">
+      <c r="E120" s="6" t="n">
         <v>28.77246760484882</v>
       </c>
-      <c r="F120" s="4" t="n">
+      <c r="F120" s="6" t="n">
         <v>71.22753239515117</v>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -3549,13 +3712,21 @@
       <c r="B121" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
+      <c r="C121" s="4" t="n">
+        <v>43127</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>12156</v>
+      </c>
+      <c r="E121" s="6" t="n">
+        <v>28.18651888608065</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>71.81348111391935</v>
+      </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -3568,13 +3739,21 @@
       <c r="B122" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C122" s="4" t="n"/>
-      <c r="D122" s="4" t="n"/>
-      <c r="E122" s="4" t="n"/>
-      <c r="F122" s="4" t="n"/>
+      <c r="C122" s="4" t="n">
+        <v>24929</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>6935</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>27.81900597697461</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>72.18099402302539</v>
+      </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -3593,10 +3772,10 @@
       <c r="D123" s="4" t="n">
         <v>4287</v>
       </c>
-      <c r="E123" s="4" t="n">
+      <c r="E123" s="6" t="n">
         <v>10.8751902587519</v>
       </c>
-      <c r="F123" s="4" t="n">
+      <c r="F123" s="6" t="n">
         <v>89.1248097412481</v>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -3620,10 +3799,10 @@
       <c r="D124" s="4" t="n">
         <v>4131</v>
       </c>
-      <c r="E124" s="4" t="n">
+      <c r="E124" s="6" t="n">
         <v>10.7382375877307</v>
       </c>
-      <c r="F124" s="4" t="n">
+      <c r="F124" s="6" t="n">
         <v>89.26176241226931</v>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -3647,10 +3826,10 @@
       <c r="D125" s="4" t="n">
         <v>4303</v>
       </c>
-      <c r="E125" s="4" t="n">
+      <c r="E125" s="6" t="n">
         <v>10.70904158681964</v>
       </c>
-      <c r="F125" s="4" t="n">
+      <c r="F125" s="6" t="n">
         <v>89.29095841318036</v>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -3674,10 +3853,10 @@
       <c r="D126" s="4" t="n">
         <v>4440</v>
       </c>
-      <c r="E126" s="4" t="n">
+      <c r="E126" s="6" t="n">
         <v>10.80002918926808</v>
       </c>
-      <c r="F126" s="4" t="n">
+      <c r="F126" s="6" t="n">
         <v>89.19997081073193</v>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -3701,10 +3880,10 @@
       <c r="D127" s="4" t="n">
         <v>2979</v>
       </c>
-      <c r="E127" s="4" t="n">
+      <c r="E127" s="6" t="n">
         <v>10.68622879075941</v>
       </c>
-      <c r="F127" s="4" t="n">
+      <c r="F127" s="6" t="n">
         <v>89.3137712092406</v>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -3728,10 +3907,10 @@
       <c r="D128" s="4" t="n">
         <v>3429</v>
       </c>
-      <c r="E128" s="4" t="n">
+      <c r="E128" s="6" t="n">
         <v>10.2985343584815</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="6" t="n">
         <v>89.7014656415185</v>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -3755,10 +3934,10 @@
       <c r="D129" s="4" t="n">
         <v>4317</v>
       </c>
-      <c r="E129" s="4" t="n">
+      <c r="E129" s="6" t="n">
         <v>9.83147346845821</v>
       </c>
-      <c r="F129" s="4" t="n">
+      <c r="F129" s="6" t="n">
         <v>90.16852653154179</v>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -3782,10 +3961,10 @@
       <c r="D130" s="4" t="n">
         <v>4080</v>
       </c>
-      <c r="E130" s="4" t="n">
+      <c r="E130" s="6" t="n">
         <v>8.483915909421722</v>
       </c>
-      <c r="F130" s="4" t="n">
+      <c r="F130" s="6" t="n">
         <v>91.51608409057827</v>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -3809,10 +3988,10 @@
       <c r="D131" s="4" t="n">
         <v>3880</v>
       </c>
-      <c r="E131" s="4" t="n">
+      <c r="E131" s="6" t="n">
         <v>7.945284023426301</v>
       </c>
-      <c r="F131" s="4" t="n">
+      <c r="F131" s="6" t="n">
         <v>92.0547159765737</v>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -3830,13 +4009,21 @@
       <c r="B132" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="n"/>
-      <c r="E132" s="4" t="n"/>
-      <c r="F132" s="4" t="n"/>
+      <c r="C132" s="4" t="n">
+        <v>52632</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>4393</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>8.346633226934184</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>91.65336677306581</v>
+      </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -3849,13 +4036,21 @@
       <c r="B133" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C133" s="4" t="n"/>
-      <c r="D133" s="4" t="n"/>
-      <c r="E133" s="4" t="n"/>
-      <c r="F133" s="4" t="n"/>
+      <c r="C133" s="4" t="n">
+        <v>29494</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>4236</v>
+      </c>
+      <c r="E133" s="6" t="n">
+        <v>14.36224316810199</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>85.63775683189802</v>
+      </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -3874,10 +4069,10 @@
       <c r="D134" s="4" t="n">
         <v>9646</v>
       </c>
-      <c r="E134" s="4" t="n">
+      <c r="E134" s="6" t="n">
         <v>17.87223004520862</v>
       </c>
-      <c r="F134" s="4" t="n">
+      <c r="F134" s="6" t="n">
         <v>82.12776995479138</v>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -3901,10 +4096,10 @@
       <c r="D135" s="4" t="n">
         <v>10177</v>
       </c>
-      <c r="E135" s="4" t="n">
+      <c r="E135" s="6" t="n">
         <v>19.05840933350812</v>
       </c>
-      <c r="F135" s="4" t="n">
+      <c r="F135" s="6" t="n">
         <v>80.94159066649188</v>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -3928,10 +4123,10 @@
       <c r="D136" s="4" t="n">
         <v>10706</v>
       </c>
-      <c r="E136" s="4" t="n">
+      <c r="E136" s="6" t="n">
         <v>20.83000953363037</v>
       </c>
-      <c r="F136" s="4" t="n">
+      <c r="F136" s="6" t="n">
         <v>79.16999046636963</v>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -3955,10 +4150,10 @@
       <c r="D137" s="4" t="n">
         <v>11249</v>
       </c>
-      <c r="E137" s="4" t="n">
+      <c r="E137" s="6" t="n">
         <v>22.20095127198089</v>
       </c>
-      <c r="F137" s="4" t="n">
+      <c r="F137" s="6" t="n">
         <v>77.7990487280191</v>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -3982,10 +4177,10 @@
       <c r="D138" s="4" t="n">
         <v>11141</v>
       </c>
-      <c r="E138" s="4" t="n">
+      <c r="E138" s="6" t="n">
         <v>24.6122917863297</v>
       </c>
-      <c r="F138" s="4" t="n">
+      <c r="F138" s="6" t="n">
         <v>75.38770821367031</v>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -4009,10 +4204,10 @@
       <c r="D139" s="4" t="n">
         <v>12057</v>
       </c>
-      <c r="E139" s="4" t="n">
+      <c r="E139" s="6" t="n">
         <v>24.66804427440309</v>
       </c>
-      <c r="F139" s="4" t="n">
+      <c r="F139" s="6" t="n">
         <v>75.33195572559691</v>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -4036,10 +4231,10 @@
       <c r="D140" s="4" t="n">
         <v>13427</v>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="E140" s="6" t="n">
         <v>24.66747501469724</v>
       </c>
-      <c r="F140" s="4" t="n">
+      <c r="F140" s="6" t="n">
         <v>75.33252498530277</v>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -4063,10 +4258,10 @@
       <c r="D141" s="4" t="n">
         <v>13798</v>
       </c>
-      <c r="E141" s="4" t="n">
+      <c r="E141" s="6" t="n">
         <v>24.93899904205903</v>
       </c>
-      <c r="F141" s="4" t="n">
+      <c r="F141" s="6" t="n">
         <v>75.06100095794096</v>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -4090,10 +4285,10 @@
       <c r="D142" s="4" t="n">
         <v>14791</v>
       </c>
-      <c r="E142" s="4" t="n">
+      <c r="E142" s="6" t="n">
         <v>26.1006899715894</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="6" t="n">
         <v>73.8993100284106</v>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -4111,13 +4306,21 @@
       <c r="B143" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="4" t="n"/>
-      <c r="F143" s="4" t="n"/>
+      <c r="C143" s="4" t="n">
+        <v>52102</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>14841</v>
+      </c>
+      <c r="E143" s="6" t="n">
+        <v>28.48451115120341</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>71.51548884879659</v>
+      </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -4130,13 +4333,21 @@
       <c r="B144" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="4" t="n"/>
-      <c r="F144" s="4" t="n"/>
+      <c r="C144" s="4" t="n">
+        <v>34947</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>8098</v>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>23.17223223738804</v>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>76.82776776261196</v>
+      </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -4155,10 +4366,10 @@
       <c r="D145" s="4" t="n">
         <v>12935</v>
       </c>
-      <c r="E145" s="4" t="n">
+      <c r="E145" s="6" t="n">
         <v>32.43643111490044</v>
       </c>
-      <c r="F145" s="4" t="n">
+      <c r="F145" s="6" t="n">
         <v>67.56356888509956</v>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -4182,10 +4393,10 @@
       <c r="D146" s="4" t="n">
         <v>12264</v>
       </c>
-      <c r="E146" s="4" t="n">
+      <c r="E146" s="6" t="n">
         <v>34.20634256547569</v>
       </c>
-      <c r="F146" s="4" t="n">
+      <c r="F146" s="6" t="n">
         <v>65.79365743452431</v>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -4209,10 +4420,10 @@
       <c r="D147" s="4" t="n">
         <v>13261</v>
       </c>
-      <c r="E147" s="4" t="n">
+      <c r="E147" s="6" t="n">
         <v>37.1279782736512</v>
       </c>
-      <c r="F147" s="4" t="n">
+      <c r="F147" s="6" t="n">
         <v>62.8720217263488</v>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -4236,10 +4447,10 @@
       <c r="D148" s="4" t="n">
         <v>12788</v>
       </c>
-      <c r="E148" s="4" t="n">
+      <c r="E148" s="6" t="n">
         <v>38.83978739559605</v>
       </c>
-      <c r="F148" s="4" t="n">
+      <c r="F148" s="6" t="n">
         <v>61.16021260440395</v>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -4263,10 +4474,10 @@
       <c r="D149" s="4" t="n">
         <v>11569</v>
       </c>
-      <c r="E149" s="4" t="n">
+      <c r="E149" s="6" t="n">
         <v>46.32974250130151</v>
       </c>
-      <c r="F149" s="4" t="n">
+      <c r="F149" s="6" t="n">
         <v>53.67025749869849</v>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -4290,10 +4501,10 @@
       <c r="D150" s="4" t="n">
         <v>13528</v>
       </c>
-      <c r="E150" s="4" t="n">
+      <c r="E150" s="6" t="n">
         <v>45.89340842012417</v>
       </c>
-      <c r="F150" s="4" t="n">
+      <c r="F150" s="6" t="n">
         <v>54.10659157987583</v>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -4317,10 +4528,10 @@
       <c r="D151" s="4" t="n">
         <v>15224</v>
       </c>
-      <c r="E151" s="4" t="n">
+      <c r="E151" s="6" t="n">
         <v>45.60404996555133</v>
       </c>
-      <c r="F151" s="4" t="n">
+      <c r="F151" s="6" t="n">
         <v>54.39595003444867</v>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -4344,10 +4555,10 @@
       <c r="D152" s="4" t="n">
         <v>15366</v>
       </c>
-      <c r="E152" s="4" t="n">
+      <c r="E152" s="6" t="n">
         <v>43.60014754703062</v>
       </c>
-      <c r="F152" s="4" t="n">
+      <c r="F152" s="6" t="n">
         <v>56.39985245296938</v>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -4371,10 +4582,10 @@
       <c r="D153" s="4" t="n">
         <v>15715</v>
       </c>
-      <c r="E153" s="4" t="n">
+      <c r="E153" s="6" t="n">
         <v>43.5101611384905</v>
       </c>
-      <c r="F153" s="4" t="n">
+      <c r="F153" s="6" t="n">
         <v>56.4898388615095</v>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -4392,13 +4603,21 @@
       <c r="B154" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C154" s="4" t="n"/>
-      <c r="D154" s="4" t="n"/>
-      <c r="E154" s="4" t="n"/>
-      <c r="F154" s="4" t="n"/>
+      <c r="C154" s="4" t="n">
+        <v>33869</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>16759</v>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>49.48182703947563</v>
+      </c>
+      <c r="F154" s="6" t="n">
+        <v>50.51817296052437</v>
+      </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -4411,13 +4630,21 @@
       <c r="B155" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C155" s="4" t="n"/>
-      <c r="D155" s="4" t="n"/>
-      <c r="E155" s="4" t="n"/>
-      <c r="F155" s="4" t="n"/>
+      <c r="C155" s="4" t="n">
+        <v>19229</v>
+      </c>
+      <c r="D155" s="4" t="n">
+        <v>9279</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>48.25523948203234</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>51.74476051796766</v>
+      </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -4436,10 +4663,10 @@
       <c r="D156" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="E156" s="4" t="n">
+      <c r="E156" s="6" t="n">
         <v>15.05576208178439</v>
       </c>
-      <c r="F156" s="4" t="n">
+      <c r="F156" s="6" t="n">
         <v>84.94423791821561</v>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -4463,10 +4690,10 @@
       <c r="D157" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="E157" s="4" t="n">
+      <c r="E157" s="6" t="n">
         <v>23.52941176470588</v>
       </c>
-      <c r="F157" s="4" t="n">
+      <c r="F157" s="6" t="n">
         <v>76.47058823529412</v>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -4490,10 +4717,10 @@
       <c r="D158" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="E158" s="4" t="n">
+      <c r="E158" s="6" t="n">
         <v>22.29617304492512</v>
       </c>
-      <c r="F158" s="4" t="n">
+      <c r="F158" s="6" t="n">
         <v>77.70382695507487</v>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -4517,10 +4744,10 @@
       <c r="D159" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="E159" s="4" t="n">
+      <c r="E159" s="6" t="n">
         <v>23.21428571428572</v>
       </c>
-      <c r="F159" s="4" t="n">
+      <c r="F159" s="6" t="n">
         <v>76.78571428571428</v>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -4544,10 +4771,10 @@
       <c r="D160" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="E160" s="4" t="n">
+      <c r="E160" s="6" t="n">
         <v>29.39814814814815</v>
       </c>
-      <c r="F160" s="4" t="n">
+      <c r="F160" s="6" t="n">
         <v>70.60185185185185</v>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -4571,10 +4798,10 @@
       <c r="D161" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="E161" s="4" t="n">
+      <c r="E161" s="6" t="n">
         <v>30.05464480874317</v>
       </c>
-      <c r="F161" s="4" t="n">
+      <c r="F161" s="6" t="n">
         <v>69.94535519125682</v>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -4598,10 +4825,10 @@
       <c r="D162" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="E162" s="4" t="n">
+      <c r="E162" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F162" s="4" t="n">
+      <c r="F162" s="6" t="n">
         <v>75</v>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -4625,10 +4852,10 @@
       <c r="D163" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="E163" s="4" t="n">
+      <c r="E163" s="6" t="n">
         <v>18.34170854271357</v>
       </c>
-      <c r="F163" s="4" t="n">
+      <c r="F163" s="6" t="n">
         <v>81.65829145728644</v>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -4652,10 +4879,10 @@
       <c r="D164" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="E164" s="4" t="n">
+      <c r="E164" s="6" t="n">
         <v>24.08026755852843</v>
       </c>
-      <c r="F164" s="4" t="n">
+      <c r="F164" s="6" t="n">
         <v>75.91973244147157</v>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -4673,13 +4900,21 @@
       <c r="B165" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C165" s="4" t="n"/>
-      <c r="D165" s="4" t="n"/>
-      <c r="E165" s="4" t="n"/>
-      <c r="F165" s="4" t="n"/>
+      <c r="C165" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="E165" s="6" t="n">
+        <v>29.85507246376812</v>
+      </c>
+      <c r="F165" s="6" t="n">
+        <v>70.14492753623188</v>
+      </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -4692,13 +4927,21 @@
       <c r="B166" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C166" s="4" t="n"/>
-      <c r="D166" s="4" t="n"/>
-      <c r="E166" s="4" t="n"/>
-      <c r="F166" s="4" t="n"/>
+      <c r="C166" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>27.80487804878049</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>72.19512195121951</v>
+      </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -4717,10 +4960,10 @@
       <c r="D167" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E167" s="6" t="n">
         <v>24.19354838709678</v>
       </c>
-      <c r="F167" s="4" t="n">
+      <c r="F167" s="6" t="n">
         <v>75.80645161290323</v>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -4744,10 +4987,10 @@
       <c r="D168" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="E168" s="4" t="n">
+      <c r="E168" s="6" t="n">
         <v>26.96296296296296</v>
       </c>
-      <c r="F168" s="4" t="n">
+      <c r="F168" s="6" t="n">
         <v>73.03703703703704</v>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -4771,10 +5014,10 @@
       <c r="D169" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="E169" s="4" t="n">
+      <c r="E169" s="6" t="n">
         <v>45.61403508771929</v>
       </c>
-      <c r="F169" s="4" t="n">
+      <c r="F169" s="6" t="n">
         <v>54.38596491228071</v>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -4798,10 +5041,10 @@
       <c r="D170" s="4" t="n">
         <v>179</v>
       </c>
-      <c r="E170" s="4" t="n">
+      <c r="E170" s="6" t="n">
         <v>37.13692946058092</v>
       </c>
-      <c r="F170" s="4" t="n">
+      <c r="F170" s="6" t="n">
         <v>62.86307053941908</v>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -4825,10 +5068,10 @@
       <c r="D171" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="E171" s="4" t="n">
+      <c r="E171" s="6" t="n">
         <v>67.28971962616822</v>
       </c>
-      <c r="F171" s="4" t="n">
+      <c r="F171" s="6" t="n">
         <v>32.71028037383178</v>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -4852,10 +5095,10 @@
       <c r="D172" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="E172" s="4" t="n">
+      <c r="E172" s="6" t="n">
         <v>76.32653061224491</v>
       </c>
-      <c r="F172" s="4" t="n">
+      <c r="F172" s="6" t="n">
         <v>23.67346938775509</v>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -4879,10 +5122,10 @@
       <c r="D173" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="E173" s="4" t="n">
+      <c r="E173" s="6" t="n">
         <v>65.85365853658537</v>
       </c>
-      <c r="F173" s="4" t="n">
+      <c r="F173" s="6" t="n">
         <v>34.14634146341463</v>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -4906,10 +5149,10 @@
       <c r="D174" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="E174" s="4" t="n">
+      <c r="E174" s="6" t="n">
         <v>75.33632286995515</v>
       </c>
-      <c r="F174" s="4" t="n">
+      <c r="F174" s="6" t="n">
         <v>24.66367713004485</v>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -4933,10 +5176,10 @@
       <c r="D175" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="E175" s="4" t="n">
+      <c r="E175" s="6" t="n">
         <v>73.23420074349443</v>
       </c>
-      <c r="F175" s="4" t="n">
+      <c r="F175" s="6" t="n">
         <v>26.76579925650557</v>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -4954,13 +5197,21 @@
       <c r="B176" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C176" s="4" t="n"/>
-      <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="4" t="n"/>
+      <c r="C176" s="4" t="n">
+        <v>223</v>
+      </c>
+      <c r="D176" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>66.81614349775785</v>
+      </c>
+      <c r="F176" s="6" t="n">
+        <v>33.18385650224215</v>
+      </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -4973,13 +5224,21 @@
       <c r="B177" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C177" s="4" t="n"/>
-      <c r="D177" s="4" t="n"/>
-      <c r="E177" s="4" t="n"/>
-      <c r="F177" s="4" t="n"/>
+      <c r="C177" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="D177" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="E177" s="6" t="n">
+        <v>37.85714285714285</v>
+      </c>
+      <c r="F177" s="6" t="n">
+        <v>62.14285714285715</v>
+      </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -4998,10 +5257,10 @@
       <c r="D178" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="E178" s="4" t="n">
+      <c r="E178" s="6" t="n">
         <v>84.33734939759037</v>
       </c>
-      <c r="F178" s="4" t="n">
+      <c r="F178" s="6" t="n">
         <v>15.66265060240963</v>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -5025,10 +5284,10 @@
       <c r="D179" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E179" s="4" t="n">
+      <c r="E179" s="6" t="n">
         <v>88.23529411764706</v>
       </c>
-      <c r="F179" s="4" t="n">
+      <c r="F179" s="6" t="n">
         <v>11.76470588235294</v>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -5052,10 +5311,10 @@
       <c r="D180" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="E180" s="4" t="n">
+      <c r="E180" s="6" t="n">
         <v>84.90566037735849</v>
       </c>
-      <c r="F180" s="4" t="n">
+      <c r="F180" s="6" t="n">
         <v>15.09433962264151</v>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -5079,10 +5338,10 @@
       <c r="D181" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E181" s="4" t="n">
+      <c r="E181" s="6" t="n">
         <v>77.41935483870968</v>
       </c>
-      <c r="F181" s="4" t="n">
+      <c r="F181" s="6" t="n">
         <v>22.58064516129032</v>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -5106,10 +5365,10 @@
       <c r="D182" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="E182" s="4" t="n">
+      <c r="E182" s="6" t="n">
         <v>79.24528301886792</v>
       </c>
-      <c r="F182" s="4" t="n">
+      <c r="F182" s="6" t="n">
         <v>20.75471698113208</v>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -5133,10 +5392,10 @@
       <c r="D183" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="E183" s="4" t="n">
+      <c r="E183" s="6" t="n">
         <v>81.15942028985508</v>
       </c>
-      <c r="F183" s="4" t="n">
+      <c r="F183" s="6" t="n">
         <v>18.84057971014492</v>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -5160,10 +5419,10 @@
       <c r="D184" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="E184" s="4" t="n">
+      <c r="E184" s="6" t="n">
         <v>84.9624060150376</v>
       </c>
-      <c r="F184" s="4" t="n">
+      <c r="F184" s="6" t="n">
         <v>15.0375939849624</v>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -5187,10 +5446,10 @@
       <c r="D185" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="E185" s="4" t="n">
+      <c r="E185" s="6" t="n">
         <v>90.56603773584906</v>
       </c>
-      <c r="F185" s="4" t="n">
+      <c r="F185" s="6" t="n">
         <v>9.433962264150935</v>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -5214,10 +5473,10 @@
       <c r="D186" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="E186" s="4" t="n">
+      <c r="E186" s="6" t="n">
         <v>93.22033898305084</v>
       </c>
-      <c r="F186" s="4" t="n">
+      <c r="F186" s="6" t="n">
         <v>6.779661016949163</v>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -5235,13 +5494,21 @@
       <c r="B187" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
-      <c r="E187" s="4" t="n"/>
-      <c r="F187" s="4" t="n"/>
+      <c r="C187" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="D187" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E187" s="6" t="n">
+        <v>71.83098591549296</v>
+      </c>
+      <c r="F187" s="6" t="n">
+        <v>28.16901408450704</v>
+      </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -5254,13 +5521,21 @@
       <c r="B188" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
-      <c r="E188" s="4" t="n"/>
-      <c r="F188" s="4" t="n"/>
+      <c r="C188" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E188" s="6" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F188" s="6" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -5279,10 +5554,10 @@
       <c r="D189" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="E189" s="4" t="n">
+      <c r="E189" s="6" t="n">
         <v>61.33333333333333</v>
       </c>
-      <c r="F189" s="4" t="n">
+      <c r="F189" s="6" t="n">
         <v>38.66666666666667</v>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -5306,10 +5581,10 @@
       <c r="D190" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E190" s="4" t="n">
+      <c r="E190" s="6" t="n">
         <v>7.721280602636535</v>
       </c>
-      <c r="F190" s="4" t="n">
+      <c r="F190" s="6" t="n">
         <v>92.27871939736346</v>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -5333,10 +5608,10 @@
       <c r="D191" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="E191" s="4" t="n">
+      <c r="E191" s="6" t="n">
         <v>9.069767441860465</v>
       </c>
-      <c r="F191" s="4" t="n">
+      <c r="F191" s="6" t="n">
         <v>90.93023255813954</v>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -5360,10 +5635,10 @@
       <c r="D192" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E192" s="4" t="n">
+      <c r="E192" s="6" t="n">
         <v>7.262569832402235</v>
       </c>
-      <c r="F192" s="4" t="n">
+      <c r="F192" s="6" t="n">
         <v>92.73743016759776</v>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -5387,10 +5662,10 @@
       <c r="D193" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E193" s="4" t="n">
+      <c r="E193" s="6" t="n">
         <v>10.6</v>
       </c>
-      <c r="F193" s="4" t="n">
+      <c r="F193" s="6" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -5414,10 +5689,10 @@
       <c r="D194" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="E194" s="4" t="n">
+      <c r="E194" s="6" t="n">
         <v>7.372654155495978</v>
       </c>
-      <c r="F194" s="4" t="n">
+      <c r="F194" s="6" t="n">
         <v>92.62734584450402</v>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -5441,10 +5716,10 @@
       <c r="D195" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="E195" s="4" t="n">
+      <c r="E195" s="6" t="n">
         <v>14.92842535787321</v>
       </c>
-      <c r="F195" s="4" t="n">
+      <c r="F195" s="6" t="n">
         <v>85.07157464212679</v>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -5468,10 +5743,10 @@
       <c r="D196" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="E196" s="4" t="n">
+      <c r="E196" s="6" t="n">
         <v>28.38283828382838</v>
       </c>
-      <c r="F196" s="4" t="n">
+      <c r="F196" s="6" t="n">
         <v>71.61716171617162</v>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -5495,10 +5770,10 @@
       <c r="D197" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="E197" s="4" t="n">
+      <c r="E197" s="6" t="n">
         <v>48.06201550387597</v>
       </c>
-      <c r="F197" s="4" t="n">
+      <c r="F197" s="6" t="n">
         <v>51.93798449612403</v>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -5516,13 +5791,21 @@
       <c r="B198" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C198" s="4" t="n"/>
-      <c r="D198" s="4" t="n"/>
-      <c r="E198" s="4" t="n"/>
-      <c r="F198" s="4" t="n"/>
+      <c r="C198" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="E198" s="6" t="n">
+        <v>32.95454545454545</v>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>67.04545454545455</v>
+      </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -5535,13 +5818,21 @@
       <c r="B199" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C199" s="4" t="n"/>
-      <c r="D199" s="4" t="n"/>
-      <c r="E199" s="4" t="n"/>
-      <c r="F199" s="4" t="n"/>
+      <c r="C199" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="D199" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="E199" s="6" t="n">
+        <v>33.76623376623377</v>
+      </c>
+      <c r="F199" s="6" t="n">
+        <v>66.23376623376623</v>
+      </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -5560,10 +5851,10 @@
       <c r="D200" s="4" t="n">
         <v>4463</v>
       </c>
-      <c r="E200" s="4" t="n">
+      <c r="E200" s="6" t="n">
         <v>42.37561716672997</v>
       </c>
-      <c r="F200" s="4" t="n">
+      <c r="F200" s="6" t="n">
         <v>57.62438283327003</v>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -5587,10 +5878,10 @@
       <c r="D201" s="4" t="n">
         <v>4790</v>
       </c>
-      <c r="E201" s="4" t="n">
+      <c r="E201" s="6" t="n">
         <v>44.12713035467527</v>
       </c>
-      <c r="F201" s="4" t="n">
+      <c r="F201" s="6" t="n">
         <v>55.87286964532473</v>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -5614,10 +5905,10 @@
       <c r="D202" s="4" t="n">
         <v>5315</v>
       </c>
-      <c r="E202" s="4" t="n">
+      <c r="E202" s="6" t="n">
         <v>47.19410406677322</v>
       </c>
-      <c r="F202" s="4" t="n">
+      <c r="F202" s="6" t="n">
         <v>52.80589593322678</v>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -5641,10 +5932,10 @@
       <c r="D203" s="4" t="n">
         <v>5333</v>
       </c>
-      <c r="E203" s="4" t="n">
+      <c r="E203" s="6" t="n">
         <v>48.20137382501808</v>
       </c>
-      <c r="F203" s="4" t="n">
+      <c r="F203" s="6" t="n">
         <v>51.79862617498192</v>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -5668,10 +5959,10 @@
       <c r="D204" s="4" t="n">
         <v>4738</v>
       </c>
-      <c r="E204" s="4" t="n">
+      <c r="E204" s="6" t="n">
         <v>48.26321686869716</v>
       </c>
-      <c r="F204" s="4" t="n">
+      <c r="F204" s="6" t="n">
         <v>51.73678313130284</v>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -5695,10 +5986,10 @@
       <c r="D205" s="4" t="n">
         <v>5081</v>
       </c>
-      <c r="E205" s="4" t="n">
+      <c r="E205" s="6" t="n">
         <v>46.2624055358281</v>
       </c>
-      <c r="F205" s="4" t="n">
+      <c r="F205" s="6" t="n">
         <v>53.7375944641719</v>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -5722,10 +6013,10 @@
       <c r="D206" s="4" t="n">
         <v>5467</v>
       </c>
-      <c r="E206" s="4" t="n">
+      <c r="E206" s="6" t="n">
         <v>46.874732058647</v>
       </c>
-      <c r="F206" s="4" t="n">
+      <c r="F206" s="6" t="n">
         <v>53.125267941353</v>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -5749,10 +6040,10 @@
       <c r="D207" s="4" t="n">
         <v>5739</v>
       </c>
-      <c r="E207" s="4" t="n">
+      <c r="E207" s="6" t="n">
         <v>47.85690460306871</v>
       </c>
-      <c r="F207" s="4" t="n">
+      <c r="F207" s="6" t="n">
         <v>52.14309539693129</v>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -5776,10 +6067,10 @@
       <c r="D208" s="4" t="n">
         <v>6142</v>
       </c>
-      <c r="E208" s="4" t="n">
+      <c r="E208" s="6" t="n">
         <v>49.63232323232323</v>
       </c>
-      <c r="F208" s="4" t="n">
+      <c r="F208" s="6" t="n">
         <v>50.36767676767677</v>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -5797,13 +6088,21 @@
       <c r="B209" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C209" s="4" t="n"/>
-      <c r="D209" s="4" t="n"/>
-      <c r="E209" s="4" t="n"/>
-      <c r="F209" s="4" t="n"/>
+      <c r="C209" s="4" t="n">
+        <v>10713</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>6358</v>
+      </c>
+      <c r="E209" s="6" t="n">
+        <v>59.34845514795109</v>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>40.65154485204891</v>
+      </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -5816,13 +6115,21 @@
       <c r="B210" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="4" t="n"/>
-      <c r="F210" s="4" t="n"/>
+      <c r="C210" s="4" t="n">
+        <v>6188</v>
+      </c>
+      <c r="D210" s="4" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E210" s="6" t="n">
+        <v>58.51648351648352</v>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>41.48351648351648</v>
+      </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -5841,10 +6148,10 @@
       <c r="D211" s="4" t="n">
         <v>5077</v>
       </c>
-      <c r="E211" s="4" t="n">
+      <c r="E211" s="6" t="n">
         <v>73.02934407364788</v>
       </c>
-      <c r="F211" s="4" t="n">
+      <c r="F211" s="6" t="n">
         <v>26.97065592635212</v>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -5868,10 +6175,10 @@
       <c r="D212" s="4" t="n">
         <v>4463</v>
       </c>
-      <c r="E212" s="4" t="n">
+      <c r="E212" s="6" t="n">
         <v>71.1461820500558</v>
       </c>
-      <c r="F212" s="4" t="n">
+      <c r="F212" s="6" t="n">
         <v>28.8538179499442</v>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -5895,10 +6202,10 @@
       <c r="D213" s="4" t="n">
         <v>4740</v>
       </c>
-      <c r="E213" s="4" t="n">
+      <c r="E213" s="6" t="n">
         <v>73.73988799004356</v>
       </c>
-      <c r="F213" s="4" t="n">
+      <c r="F213" s="6" t="n">
         <v>26.26011200995644</v>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -5922,10 +6229,10 @@
       <c r="D214" s="4" t="n">
         <v>4525</v>
       </c>
-      <c r="E214" s="4" t="n">
+      <c r="E214" s="6" t="n">
         <v>71.28229363579081</v>
       </c>
-      <c r="F214" s="4" t="n">
+      <c r="F214" s="6" t="n">
         <v>28.71770636420919</v>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -5949,10 +6256,10 @@
       <c r="D215" s="4" t="n">
         <v>3898</v>
       </c>
-      <c r="E215" s="4" t="n">
+      <c r="E215" s="6" t="n">
         <v>74.91831635594849</v>
       </c>
-      <c r="F215" s="4" t="n">
+      <c r="F215" s="6" t="n">
         <v>25.08168364405151</v>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -5976,10 +6283,10 @@
       <c r="D216" s="4" t="n">
         <v>4589</v>
       </c>
-      <c r="E216" s="4" t="n">
+      <c r="E216" s="6" t="n">
         <v>78.16385624254811</v>
       </c>
-      <c r="F216" s="4" t="n">
+      <c r="F216" s="6" t="n">
         <v>21.83614375745189</v>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -6003,10 +6310,10 @@
       <c r="D217" s="4" t="n">
         <v>4756</v>
       </c>
-      <c r="E217" s="4" t="n">
+      <c r="E217" s="6" t="n">
         <v>77.48452264581297</v>
       </c>
-      <c r="F217" s="4" t="n">
+      <c r="F217" s="6" t="n">
         <v>22.51547735418703</v>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -6030,10 +6337,10 @@
       <c r="D218" s="4" t="n">
         <v>4829</v>
       </c>
-      <c r="E218" s="4" t="n">
+      <c r="E218" s="6" t="n">
         <v>77.02982931887064</v>
       </c>
-      <c r="F218" s="4" t="n">
+      <c r="F218" s="6" t="n">
         <v>22.97017068112936</v>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -6057,10 +6364,10 @@
       <c r="D219" s="4" t="n">
         <v>4759</v>
       </c>
-      <c r="E219" s="4" t="n">
+      <c r="E219" s="6" t="n">
         <v>78.49249546429161</v>
       </c>
-      <c r="F219" s="4" t="n">
+      <c r="F219" s="6" t="n">
         <v>21.50750453570839</v>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -6078,13 +6385,21 @@
       <c r="B220" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C220" s="4" t="n"/>
-      <c r="D220" s="4" t="n"/>
-      <c r="E220" s="4" t="n"/>
-      <c r="F220" s="4" t="n"/>
+      <c r="C220" s="4" t="n">
+        <v>4254</v>
+      </c>
+      <c r="D220" s="4" t="n">
+        <v>3062</v>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>71.97931358721203</v>
+      </c>
+      <c r="F220" s="6" t="n">
+        <v>28.02068641278797</v>
+      </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -6097,13 +6412,21 @@
       <c r="B221" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C221" s="4" t="n"/>
-      <c r="D221" s="4" t="n"/>
-      <c r="E221" s="4" t="n"/>
-      <c r="F221" s="4" t="n"/>
+      <c r="C221" s="4" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D221" s="4" t="n">
+        <v>1396</v>
+      </c>
+      <c r="E221" s="6" t="n">
+        <v>72.14470284237726</v>
+      </c>
+      <c r="F221" s="6" t="n">
+        <v>27.85529715762274</v>
+      </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -6122,10 +6445,10 @@
       <c r="D222" s="4" t="n">
         <v>10465</v>
       </c>
-      <c r="E222" s="4" t="n">
+      <c r="E222" s="6" t="n">
         <v>45.36980837596462</v>
       </c>
-      <c r="F222" s="4" t="n">
+      <c r="F222" s="6" t="n">
         <v>54.63019162403538</v>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -6149,10 +6472,10 @@
       <c r="D223" s="4" t="n">
         <v>10444</v>
       </c>
-      <c r="E223" s="4" t="n">
+      <c r="E223" s="6" t="n">
         <v>47.23227206946454</v>
       </c>
-      <c r="F223" s="4" t="n">
+      <c r="F223" s="6" t="n">
         <v>52.76772793053546</v>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -6176,10 +6499,10 @@
       <c r="D224" s="4" t="n">
         <v>10320</v>
       </c>
-      <c r="E224" s="4" t="n">
+      <c r="E224" s="6" t="n">
         <v>47.46355148783516</v>
       </c>
-      <c r="F224" s="4" t="n">
+      <c r="F224" s="6" t="n">
         <v>52.53644851216484</v>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -6203,10 +6526,10 @@
       <c r="D225" s="4" t="n">
         <v>10563</v>
       </c>
-      <c r="E225" s="4" t="n">
+      <c r="E225" s="6" t="n">
         <v>44.98722316865418</v>
       </c>
-      <c r="F225" s="4" t="n">
+      <c r="F225" s="6" t="n">
         <v>55.01277683134582</v>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -6230,10 +6553,10 @@
       <c r="D226" s="4" t="n">
         <v>9250</v>
       </c>
-      <c r="E226" s="4" t="n">
+      <c r="E226" s="6" t="n">
         <v>48.39384744166579</v>
       </c>
-      <c r="F226" s="4" t="n">
+      <c r="F226" s="6" t="n">
         <v>51.60615255833421</v>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -6257,10 +6580,10 @@
       <c r="D227" s="4" t="n">
         <v>10043</v>
       </c>
-      <c r="E227" s="4" t="n">
+      <c r="E227" s="6" t="n">
         <v>47.9356593957329</v>
       </c>
-      <c r="F227" s="4" t="n">
+      <c r="F227" s="6" t="n">
         <v>52.0643406042671</v>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -6284,10 +6607,10 @@
       <c r="D228" s="4" t="n">
         <v>11104</v>
       </c>
-      <c r="E228" s="4" t="n">
+      <c r="E228" s="6" t="n">
         <v>47.02295248581351</v>
       </c>
-      <c r="F228" s="4" t="n">
+      <c r="F228" s="6" t="n">
         <v>52.97704751418649</v>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -6311,10 +6634,10 @@
       <c r="D229" s="4" t="n">
         <v>11762</v>
       </c>
-      <c r="E229" s="4" t="n">
+      <c r="E229" s="6" t="n">
         <v>47.63100348262736</v>
       </c>
-      <c r="F229" s="4" t="n">
+      <c r="F229" s="6" t="n">
         <v>52.36899651737264</v>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -6338,10 +6661,10 @@
       <c r="D230" s="4" t="n">
         <v>11790</v>
       </c>
-      <c r="E230" s="4" t="n">
+      <c r="E230" s="6" t="n">
         <v>47.46758998309043</v>
       </c>
-      <c r="F230" s="4" t="n">
+      <c r="F230" s="6" t="n">
         <v>52.53241001690957</v>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -6359,13 +6682,21 @@
       <c r="B231" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C231" s="4" t="n"/>
-      <c r="D231" s="4" t="n"/>
-      <c r="E231" s="4" t="n"/>
-      <c r="F231" s="4" t="n"/>
+      <c r="C231" s="4" t="n">
+        <v>33590</v>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>12493</v>
+      </c>
+      <c r="E231" s="6" t="n">
+        <v>37.19261685025305</v>
+      </c>
+      <c r="F231" s="6" t="n">
+        <v>62.80738314974695</v>
+      </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -6378,13 +6709,21 @@
       <c r="B232" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C232" s="4" t="n"/>
-      <c r="D232" s="4" t="n"/>
-      <c r="E232" s="4" t="n"/>
-      <c r="F232" s="4" t="n"/>
+      <c r="C232" s="4" t="n">
+        <v>14522</v>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>6893</v>
+      </c>
+      <c r="E232" s="6" t="n">
+        <v>47.46591378597989</v>
+      </c>
+      <c r="F232" s="6" t="n">
+        <v>52.53408621402011</v>
+      </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -6403,10 +6742,10 @@
       <c r="D233" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E233" s="4" t="n">
+      <c r="E233" s="6" t="n">
         <v>40.47619047619047</v>
       </c>
-      <c r="F233" s="4" t="n">
+      <c r="F233" s="6" t="n">
         <v>59.52380952380953</v>
       </c>
       <c r="G233" s="4" t="inlineStr">
@@ -6430,10 +6769,10 @@
       <c r="D234" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E234" s="4" t="n">
+      <c r="E234" s="6" t="n">
         <v>39.79591836734694</v>
       </c>
-      <c r="F234" s="4" t="n">
+      <c r="F234" s="6" t="n">
         <v>60.20408163265306</v>
       </c>
       <c r="G234" s="4" t="inlineStr">
@@ -6457,10 +6796,10 @@
       <c r="D235" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E235" s="4" t="n">
+      <c r="E235" s="6" t="n">
         <v>47.22222222222222</v>
       </c>
-      <c r="F235" s="4" t="n">
+      <c r="F235" s="6" t="n">
         <v>52.77777777777778</v>
       </c>
       <c r="G235" s="4" t="inlineStr">
@@ -6484,10 +6823,10 @@
       <c r="D236" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="E236" s="4" t="n">
+      <c r="E236" s="6" t="n">
         <v>45.06172839506173</v>
       </c>
-      <c r="F236" s="4" t="n">
+      <c r="F236" s="6" t="n">
         <v>54.93827160493827</v>
       </c>
       <c r="G236" s="4" t="inlineStr">
@@ -6511,10 +6850,10 @@
       <c r="D237" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="E237" s="4" t="n">
+      <c r="E237" s="6" t="n">
         <v>34.05797101449276</v>
       </c>
-      <c r="F237" s="4" t="n">
+      <c r="F237" s="6" t="n">
         <v>65.94202898550725</v>
       </c>
       <c r="G237" s="4" t="inlineStr">
@@ -6538,10 +6877,10 @@
       <c r="D238" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="E238" s="4" t="n">
+      <c r="E238" s="6" t="n">
         <v>36.12903225806451</v>
       </c>
-      <c r="F238" s="4" t="n">
+      <c r="F238" s="6" t="n">
         <v>63.87096774193549</v>
       </c>
       <c r="G238" s="4" t="inlineStr">
@@ -6565,10 +6904,10 @@
       <c r="D239" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="E239" s="4" t="n">
+      <c r="E239" s="6" t="n">
         <v>43.60189573459716</v>
       </c>
-      <c r="F239" s="4" t="n">
+      <c r="F239" s="6" t="n">
         <v>56.39810426540284</v>
       </c>
       <c r="G239" s="4" t="inlineStr">
@@ -6592,10 +6931,10 @@
       <c r="D240" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="E240" s="4" t="n">
+      <c r="E240" s="6" t="n">
         <v>31.31868131868132</v>
       </c>
-      <c r="F240" s="4" t="n">
+      <c r="F240" s="6" t="n">
         <v>68.68131868131869</v>
       </c>
       <c r="G240" s="4" t="inlineStr">
@@ -6619,10 +6958,10 @@
       <c r="D241" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="E241" s="4" t="n">
+      <c r="E241" s="6" t="n">
         <v>44.96644295302013</v>
       </c>
-      <c r="F241" s="4" t="n">
+      <c r="F241" s="6" t="n">
         <v>55.03355704697987</v>
       </c>
       <c r="G241" s="4" t="inlineStr">
@@ -6640,13 +6979,21 @@
       <c r="B242" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C242" s="4" t="n"/>
-      <c r="D242" s="4" t="n"/>
-      <c r="E242" s="4" t="n"/>
-      <c r="F242" s="4" t="n"/>
+      <c r="C242" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="E242" s="6" t="n">
+        <v>51.06382978723404</v>
+      </c>
+      <c r="F242" s="6" t="n">
+        <v>48.93617021276596</v>
+      </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -6659,13 +7006,21 @@
       <c r="B243" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C243" s="4" t="n"/>
-      <c r="D243" s="4" t="n"/>
-      <c r="E243" s="4" t="n"/>
-      <c r="F243" s="4" t="n"/>
+      <c r="C243" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="D243" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E243" s="6" t="n">
+        <v>41.66666666666667</v>
+      </c>
+      <c r="F243" s="6" t="n">
+        <v>58.33333333333333</v>
+      </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -6684,10 +7039,10 @@
       <c r="D244" s="4" t="n">
         <v>17218</v>
       </c>
-      <c r="E244" s="4" t="n">
+      <c r="E244" s="6" t="n">
         <v>24.10438045106466</v>
       </c>
-      <c r="F244" s="4" t="n">
+      <c r="F244" s="6" t="n">
         <v>75.89561954893534</v>
       </c>
       <c r="G244" s="4" t="inlineStr">
@@ -6711,10 +7066,10 @@
       <c r="D245" s="4" t="n">
         <v>16157</v>
       </c>
-      <c r="E245" s="4" t="n">
+      <c r="E245" s="6" t="n">
         <v>24.64384857081846</v>
       </c>
-      <c r="F245" s="4" t="n">
+      <c r="F245" s="6" t="n">
         <v>75.35615142918154</v>
       </c>
       <c r="G245" s="4" t="inlineStr">
@@ -6738,10 +7093,10 @@
       <c r="D246" s="4" t="n">
         <v>18392</v>
       </c>
-      <c r="E246" s="4" t="n">
+      <c r="E246" s="6" t="n">
         <v>27.33691047726631</v>
       </c>
-      <c r="F246" s="4" t="n">
+      <c r="F246" s="6" t="n">
         <v>72.66308952273369</v>
       </c>
       <c r="G246" s="4" t="inlineStr">
@@ -6765,10 +7120,10 @@
       <c r="D247" s="4" t="n">
         <v>18129</v>
       </c>
-      <c r="E247" s="4" t="n">
+      <c r="E247" s="6" t="n">
         <v>28.92079444843264</v>
       </c>
-      <c r="F247" s="4" t="n">
+      <c r="F247" s="6" t="n">
         <v>71.07920555156736</v>
       </c>
       <c r="G247" s="4" t="inlineStr">
@@ -6792,10 +7147,10 @@
       <c r="D248" s="4" t="n">
         <v>14527</v>
       </c>
-      <c r="E248" s="4" t="n">
+      <c r="E248" s="6" t="n">
         <v>29.1449321884279</v>
       </c>
-      <c r="F248" s="4" t="n">
+      <c r="F248" s="6" t="n">
         <v>70.8550678115721</v>
       </c>
       <c r="G248" s="4" t="inlineStr">
@@ -6819,10 +7174,10 @@
       <c r="D249" s="4" t="n">
         <v>15384</v>
       </c>
-      <c r="E249" s="4" t="n">
+      <c r="E249" s="6" t="n">
         <v>27.62831794834956</v>
       </c>
-      <c r="F249" s="4" t="n">
+      <c r="F249" s="6" t="n">
         <v>72.37168205165044</v>
       </c>
       <c r="G249" s="4" t="inlineStr">
@@ -6846,10 +7201,10 @@
       <c r="D250" s="4" t="n">
         <v>17884</v>
       </c>
-      <c r="E250" s="4" t="n">
+      <c r="E250" s="6" t="n">
         <v>27.89797987676468</v>
       </c>
-      <c r="F250" s="4" t="n">
+      <c r="F250" s="6" t="n">
         <v>72.10202012323532</v>
       </c>
       <c r="G250" s="4" t="inlineStr">
@@ -6873,10 +7228,10 @@
       <c r="D251" s="4" t="n">
         <v>18347</v>
       </c>
-      <c r="E251" s="4" t="n">
+      <c r="E251" s="6" t="n">
         <v>27.29680270185827</v>
       </c>
-      <c r="F251" s="4" t="n">
+      <c r="F251" s="6" t="n">
         <v>72.70319729814173</v>
       </c>
       <c r="G251" s="4" t="inlineStr">
@@ -6900,10 +7255,10 @@
       <c r="D252" s="4" t="n">
         <v>18449</v>
       </c>
-      <c r="E252" s="4" t="n">
+      <c r="E252" s="6" t="n">
         <v>27.32132808103545</v>
       </c>
-      <c r="F252" s="4" t="n">
+      <c r="F252" s="6" t="n">
         <v>72.67867191896455</v>
       </c>
       <c r="G252" s="4" t="inlineStr">
@@ -6921,13 +7276,21 @@
       <c r="B253" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C253" s="4" t="n"/>
-      <c r="D253" s="4" t="n"/>
-      <c r="E253" s="4" t="n"/>
-      <c r="F253" s="4" t="n"/>
+      <c r="C253" s="4" t="n">
+        <v>71195</v>
+      </c>
+      <c r="D253" s="4" t="n">
+        <v>18511</v>
+      </c>
+      <c r="E253" s="6" t="n">
+        <v>26.00042137790575</v>
+      </c>
+      <c r="F253" s="6" t="n">
+        <v>73.99957862209425</v>
+      </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -6940,13 +7303,21 @@
       <c r="B254" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C254" s="4" t="n"/>
-      <c r="D254" s="4" t="n"/>
-      <c r="E254" s="4" t="n"/>
-      <c r="F254" s="4" t="n"/>
+      <c r="C254" s="4" t="n">
+        <v>39666</v>
+      </c>
+      <c r="D254" s="4" t="n">
+        <v>10298</v>
+      </c>
+      <c r="E254" s="6" t="n">
+        <v>25.96178087026673</v>
+      </c>
+      <c r="F254" s="6" t="n">
+        <v>74.03821912973328</v>
+      </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -6965,10 +7336,10 @@
       <c r="D255" s="4" t="n">
         <v>7219</v>
       </c>
-      <c r="E255" s="4" t="n">
+      <c r="E255" s="6" t="n">
         <v>31.64701240629521</v>
       </c>
-      <c r="F255" s="4" t="n">
+      <c r="F255" s="6" t="n">
         <v>68.3529875937048</v>
       </c>
       <c r="G255" s="4" t="inlineStr">
@@ -6992,10 +7363,10 @@
       <c r="D256" s="4" t="n">
         <v>6596</v>
       </c>
-      <c r="E256" s="4" t="n">
+      <c r="E256" s="6" t="n">
         <v>29.33641700764989</v>
       </c>
-      <c r="F256" s="4" t="n">
+      <c r="F256" s="6" t="n">
         <v>70.66358299235011</v>
       </c>
       <c r="G256" s="4" t="inlineStr">
@@ -7019,10 +7390,10 @@
       <c r="D257" s="4" t="n">
         <v>6603</v>
       </c>
-      <c r="E257" s="4" t="n">
+      <c r="E257" s="6" t="n">
         <v>29.70310391363023</v>
       </c>
-      <c r="F257" s="4" t="n">
+      <c r="F257" s="6" t="n">
         <v>70.29689608636977</v>
       </c>
       <c r="G257" s="4" t="inlineStr">
@@ -7046,10 +7417,10 @@
       <c r="D258" s="4" t="n">
         <v>6964</v>
       </c>
-      <c r="E258" s="4" t="n">
+      <c r="E258" s="6" t="n">
         <v>32.28558182661103</v>
       </c>
-      <c r="F258" s="4" t="n">
+      <c r="F258" s="6" t="n">
         <v>67.71441817338896</v>
       </c>
       <c r="G258" s="4" t="inlineStr">
@@ -7073,10 +7444,10 @@
       <c r="D259" s="4" t="n">
         <v>6882</v>
       </c>
-      <c r="E259" s="4" t="n">
+      <c r="E259" s="6" t="n">
         <v>35.89609847694555</v>
       </c>
-      <c r="F259" s="4" t="n">
+      <c r="F259" s="6" t="n">
         <v>64.10390152305445</v>
       </c>
       <c r="G259" s="4" t="inlineStr">
@@ -7100,10 +7471,10 @@
       <c r="D260" s="4" t="n">
         <v>7557</v>
       </c>
-      <c r="E260" s="4" t="n">
+      <c r="E260" s="6" t="n">
         <v>35.45390570021112</v>
       </c>
-      <c r="F260" s="4" t="n">
+      <c r="F260" s="6" t="n">
         <v>64.54609429978888</v>
       </c>
       <c r="G260" s="4" t="inlineStr">
@@ -7127,10 +7498,10 @@
       <c r="D261" s="4" t="n">
         <v>7559</v>
       </c>
-      <c r="E261" s="4" t="n">
+      <c r="E261" s="6" t="n">
         <v>34.96461445950321</v>
       </c>
-      <c r="F261" s="4" t="n">
+      <c r="F261" s="6" t="n">
         <v>65.03538554049679</v>
       </c>
       <c r="G261" s="4" t="inlineStr">
@@ -7154,10 +7525,10 @@
       <c r="D262" s="4" t="n">
         <v>7660</v>
       </c>
-      <c r="E262" s="4" t="n">
+      <c r="E262" s="6" t="n">
         <v>33.44540016591713</v>
       </c>
-      <c r="F262" s="4" t="n">
+      <c r="F262" s="6" t="n">
         <v>66.55459983408286</v>
       </c>
       <c r="G262" s="4" t="inlineStr">
@@ -7181,10 +7552,10 @@
       <c r="D263" s="4" t="n">
         <v>7949</v>
       </c>
-      <c r="E263" s="4" t="n">
+      <c r="E263" s="6" t="n">
         <v>30.58954821827138</v>
       </c>
-      <c r="F263" s="4" t="n">
+      <c r="F263" s="6" t="n">
         <v>69.41045178172863</v>
       </c>
       <c r="G263" s="4" t="inlineStr">
@@ -7202,13 +7573,21 @@
       <c r="B264" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C264" s="4" t="n"/>
-      <c r="D264" s="4" t="n"/>
-      <c r="E264" s="4" t="n"/>
-      <c r="F264" s="4" t="n"/>
+      <c r="C264" s="4" t="n">
+        <v>25986</v>
+      </c>
+      <c r="D264" s="4" t="n">
+        <v>8484</v>
+      </c>
+      <c r="E264" s="6" t="n">
+        <v>32.6483491110598</v>
+      </c>
+      <c r="F264" s="6" t="n">
+        <v>67.3516508889402</v>
+      </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -7221,13 +7600,21 @@
       <c r="B265" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C265" s="4" t="n"/>
-      <c r="D265" s="4" t="n"/>
-      <c r="E265" s="4" t="n"/>
-      <c r="F265" s="4" t="n"/>
+      <c r="C265" s="4" t="n">
+        <v>16179</v>
+      </c>
+      <c r="D265" s="4" t="n">
+        <v>4452</v>
+      </c>
+      <c r="E265" s="6" t="n">
+        <v>27.5171518635268</v>
+      </c>
+      <c r="F265" s="6" t="n">
+        <v>72.48284813647321</v>
+      </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -7246,10 +7633,10 @@
       <c r="D266" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="E266" s="4" t="n">
+      <c r="E266" s="6" t="n">
         <v>31.05924596050269</v>
       </c>
-      <c r="F266" s="4" t="n">
+      <c r="F266" s="6" t="n">
         <v>68.94075403949731</v>
       </c>
       <c r="G266" s="4" t="inlineStr">
@@ -7273,10 +7660,10 @@
       <c r="D267" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="E267" s="4" t="n">
+      <c r="E267" s="6" t="n">
         <v>32.0079522862823</v>
       </c>
-      <c r="F267" s="4" t="n">
+      <c r="F267" s="6" t="n">
         <v>67.9920477137177</v>
       </c>
       <c r="G267" s="4" t="inlineStr">
@@ -7300,10 +7687,10 @@
       <c r="D268" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="E268" s="4" t="n">
+      <c r="E268" s="6" t="n">
         <v>38.58695652173913</v>
       </c>
-      <c r="F268" s="4" t="n">
+      <c r="F268" s="6" t="n">
         <v>61.41304347826087</v>
       </c>
       <c r="G268" s="4" t="inlineStr">
@@ -7327,10 +7714,10 @@
       <c r="D269" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="E269" s="4" t="n">
+      <c r="E269" s="6" t="n">
         <v>36.48854961832061</v>
       </c>
-      <c r="F269" s="4" t="n">
+      <c r="F269" s="6" t="n">
         <v>63.51145038167939</v>
       </c>
       <c r="G269" s="4" t="inlineStr">
@@ -7354,10 +7741,10 @@
       <c r="D270" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="E270" s="4" t="n">
+      <c r="E270" s="6" t="n">
         <v>41.20171673819743</v>
       </c>
-      <c r="F270" s="4" t="n">
+      <c r="F270" s="6" t="n">
         <v>58.79828326180257</v>
       </c>
       <c r="G270" s="4" t="inlineStr">
@@ -7381,10 +7768,10 @@
       <c r="D271" s="4" t="n">
         <v>194</v>
       </c>
-      <c r="E271" s="4" t="n">
+      <c r="E271" s="6" t="n">
         <v>40.50104384133611</v>
       </c>
-      <c r="F271" s="4" t="n">
+      <c r="F271" s="6" t="n">
         <v>59.49895615866389</v>
       </c>
       <c r="G271" s="4" t="inlineStr">
@@ -7408,10 +7795,10 @@
       <c r="D272" s="4" t="n">
         <v>241</v>
       </c>
-      <c r="E272" s="4" t="n">
+      <c r="E272" s="6" t="n">
         <v>41.91304347826087</v>
       </c>
-      <c r="F272" s="4" t="n">
+      <c r="F272" s="6" t="n">
         <v>58.08695652173913</v>
       </c>
       <c r="G272" s="4" t="inlineStr">
@@ -7435,10 +7822,10 @@
       <c r="D273" s="4" t="n">
         <v>261</v>
       </c>
-      <c r="E273" s="4" t="n">
+      <c r="E273" s="6" t="n">
         <v>45.23396880415945</v>
       </c>
-      <c r="F273" s="4" t="n">
+      <c r="F273" s="6" t="n">
         <v>54.76603119584055</v>
       </c>
       <c r="G273" s="4" t="inlineStr">
@@ -7462,10 +7849,10 @@
       <c r="D274" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="E274" s="4" t="n">
+      <c r="E274" s="6" t="n">
         <v>39.10034602076124</v>
       </c>
-      <c r="F274" s="4" t="n">
+      <c r="F274" s="6" t="n">
         <v>60.89965397923876</v>
       </c>
       <c r="G274" s="4" t="inlineStr">
@@ -7483,13 +7870,21 @@
       <c r="B275" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C275" s="4" t="n"/>
-      <c r="D275" s="4" t="n"/>
-      <c r="E275" s="4" t="n"/>
-      <c r="F275" s="4" t="n"/>
+      <c r="C275" s="4" t="n">
+        <v>477</v>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="E275" s="6" t="n">
+        <v>46.9601677148847</v>
+      </c>
+      <c r="F275" s="6" t="n">
+        <v>53.0398322851153</v>
+      </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -7502,13 +7897,21 @@
       <c r="B276" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C276" s="4" t="n"/>
-      <c r="D276" s="4" t="n"/>
-      <c r="E276" s="4" t="n"/>
-      <c r="F276" s="4" t="n"/>
+      <c r="C276" s="4" t="n">
+        <v>517</v>
+      </c>
+      <c r="D276" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="E276" s="6" t="n">
+        <v>22.63056092843327</v>
+      </c>
+      <c r="F276" s="6" t="n">
+        <v>77.36943907156673</v>
+      </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -7527,10 +7930,10 @@
       <c r="D277" s="4" t="n">
         <v>962</v>
       </c>
-      <c r="E277" s="4" t="n">
+      <c r="E277" s="6" t="n">
         <v>60.46511627906976</v>
       </c>
-      <c r="F277" s="4" t="n">
+      <c r="F277" s="6" t="n">
         <v>39.53488372093024</v>
       </c>
       <c r="G277" s="4" t="inlineStr">
@@ -7554,10 +7957,10 @@
       <c r="D278" s="4" t="n">
         <v>942</v>
       </c>
-      <c r="E278" s="4" t="n">
+      <c r="E278" s="6" t="n">
         <v>58.76481597005615</v>
       </c>
-      <c r="F278" s="4" t="n">
+      <c r="F278" s="6" t="n">
         <v>41.23518402994385</v>
       </c>
       <c r="G278" s="4" t="inlineStr">
@@ -7581,10 +7984,10 @@
       <c r="D279" s="4" t="n">
         <v>1047</v>
       </c>
-      <c r="E279" s="4" t="n">
+      <c r="E279" s="6" t="n">
         <v>71.32152588555857</v>
       </c>
-      <c r="F279" s="4" t="n">
+      <c r="F279" s="6" t="n">
         <v>28.67847411444143</v>
       </c>
       <c r="G279" s="4" t="inlineStr">
@@ -7608,10 +8011,10 @@
       <c r="D280" s="4" t="n">
         <v>867</v>
       </c>
-      <c r="E280" s="4" t="n">
+      <c r="E280" s="6" t="n">
         <v>64.12721893491124</v>
       </c>
-      <c r="F280" s="4" t="n">
+      <c r="F280" s="6" t="n">
         <v>35.87278106508876</v>
       </c>
       <c r="G280" s="4" t="inlineStr">
@@ -7635,10 +8038,10 @@
       <c r="D281" s="4" t="n">
         <v>674</v>
       </c>
-      <c r="E281" s="4" t="n">
+      <c r="E281" s="6" t="n">
         <v>64.74543707973103</v>
       </c>
-      <c r="F281" s="4" t="n">
+      <c r="F281" s="6" t="n">
         <v>35.25456292026897</v>
       </c>
       <c r="G281" s="4" t="inlineStr">
@@ -7662,10 +8065,10 @@
       <c r="D282" s="4" t="n">
         <v>820</v>
       </c>
-      <c r="E282" s="4" t="n">
+      <c r="E282" s="6" t="n">
         <v>58.36298932384341</v>
       </c>
-      <c r="F282" s="4" t="n">
+      <c r="F282" s="6" t="n">
         <v>41.63701067615659</v>
       </c>
       <c r="G282" s="4" t="inlineStr">
@@ -7689,10 +8092,10 @@
       <c r="D283" s="4" t="n">
         <v>1042</v>
       </c>
-      <c r="E283" s="4" t="n">
+      <c r="E283" s="6" t="n">
         <v>62.24611708482676</v>
       </c>
-      <c r="F283" s="4" t="n">
+      <c r="F283" s="6" t="n">
         <v>37.75388291517324</v>
       </c>
       <c r="G283" s="4" t="inlineStr">
@@ -7716,10 +8119,10 @@
       <c r="D284" s="4" t="n">
         <v>1054</v>
       </c>
-      <c r="E284" s="4" t="n">
+      <c r="E284" s="6" t="n">
         <v>62.32998225901834</v>
       </c>
-      <c r="F284" s="4" t="n">
+      <c r="F284" s="6" t="n">
         <v>37.67001774098166</v>
       </c>
       <c r="G284" s="4" t="inlineStr">
@@ -7743,10 +8146,10 @@
       <c r="D285" s="4" t="n">
         <v>1090</v>
       </c>
-      <c r="E285" s="4" t="n">
+      <c r="E285" s="6" t="n">
         <v>62.39267315397825</v>
       </c>
-      <c r="F285" s="4" t="n">
+      <c r="F285" s="6" t="n">
         <v>37.60732684602175</v>
       </c>
       <c r="G285" s="4" t="inlineStr">
@@ -7764,13 +8167,21 @@
       <c r="B286" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C286" s="4" t="n"/>
-      <c r="D286" s="4" t="n"/>
-      <c r="E286" s="4" t="n"/>
-      <c r="F286" s="4" t="n"/>
+      <c r="C286" s="4" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>1288</v>
+      </c>
+      <c r="E286" s="6" t="n">
+        <v>66.70119109269808</v>
+      </c>
+      <c r="F286" s="6" t="n">
+        <v>33.29880890730192</v>
+      </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -7783,13 +8194,21 @@
       <c r="B287" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C287" s="4" t="n"/>
-      <c r="D287" s="4" t="n"/>
-      <c r="E287" s="4" t="n"/>
-      <c r="F287" s="4" t="n"/>
+      <c r="C287" s="4" t="n">
+        <v>1238</v>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>759</v>
+      </c>
+      <c r="E287" s="6" t="n">
+        <v>61.30856219709209</v>
+      </c>
+      <c r="F287" s="6" t="n">
+        <v>38.69143780290791</v>
+      </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -7808,10 +8227,10 @@
       <c r="D288" s="4" t="n">
         <v>19320</v>
       </c>
-      <c r="E288" s="4" t="n">
+      <c r="E288" s="6" t="n">
         <v>54.25137594069415</v>
       </c>
-      <c r="F288" s="4" t="n">
+      <c r="F288" s="6" t="n">
         <v>45.74862405930585</v>
       </c>
       <c r="G288" s="4" t="inlineStr">
@@ -7835,10 +8254,10 @@
       <c r="D289" s="4" t="n">
         <v>20124</v>
       </c>
-      <c r="E289" s="4" t="n">
+      <c r="E289" s="6" t="n">
         <v>51.88871412732383</v>
       </c>
-      <c r="F289" s="4" t="n">
+      <c r="F289" s="6" t="n">
         <v>48.11128587267617</v>
       </c>
       <c r="G289" s="4" t="inlineStr">
@@ -7862,10 +8281,10 @@
       <c r="D290" s="4" t="n">
         <v>22256</v>
       </c>
-      <c r="E290" s="4" t="n">
+      <c r="E290" s="6" t="n">
         <v>52.28340537492953</v>
       </c>
-      <c r="F290" s="4" t="n">
+      <c r="F290" s="6" t="n">
         <v>47.71659462507047</v>
       </c>
       <c r="G290" s="4" t="inlineStr">
@@ -7889,10 +8308,10 @@
       <c r="D291" s="4" t="n">
         <v>22655</v>
       </c>
-      <c r="E291" s="4" t="n">
+      <c r="E291" s="6" t="n">
         <v>53.21572864793761</v>
       </c>
-      <c r="F291" s="4" t="n">
+      <c r="F291" s="6" t="n">
         <v>46.78427135206239</v>
       </c>
       <c r="G291" s="4" t="inlineStr">
@@ -7916,10 +8335,10 @@
       <c r="D292" s="4" t="n">
         <v>19149</v>
       </c>
-      <c r="E292" s="4" t="n">
+      <c r="E292" s="6" t="n">
         <v>55.92091814385422</v>
       </c>
-      <c r="F292" s="4" t="n">
+      <c r="F292" s="6" t="n">
         <v>44.07908185614578</v>
       </c>
       <c r="G292" s="4" t="inlineStr">
@@ -7943,10 +8362,10 @@
       <c r="D293" s="4" t="n">
         <v>21227</v>
       </c>
-      <c r="E293" s="4" t="n">
+      <c r="E293" s="6" t="n">
         <v>56.26176150971401</v>
       </c>
-      <c r="F293" s="4" t="n">
+      <c r="F293" s="6" t="n">
         <v>43.73823849028599</v>
       </c>
       <c r="G293" s="4" t="inlineStr">
@@ -7970,10 +8389,10 @@
       <c r="D294" s="4" t="n">
         <v>22595</v>
       </c>
-      <c r="E294" s="4" t="n">
+      <c r="E294" s="6" t="n">
         <v>54.1249461026206</v>
       </c>
-      <c r="F294" s="4" t="n">
+      <c r="F294" s="6" t="n">
         <v>45.8750538973794</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -7997,10 +8416,10 @@
       <c r="D295" s="4" t="n">
         <v>23652</v>
       </c>
-      <c r="E295" s="4" t="n">
+      <c r="E295" s="6" t="n">
         <v>53.10998338348229</v>
       </c>
-      <c r="F295" s="4" t="n">
+      <c r="F295" s="6" t="n">
         <v>46.89001661651771</v>
       </c>
       <c r="G295" s="4" t="inlineStr">
@@ -8024,10 +8443,10 @@
       <c r="D296" s="4" t="n">
         <v>24118</v>
       </c>
-      <c r="E296" s="4" t="n">
+      <c r="E296" s="6" t="n">
         <v>52.37123251976027</v>
       </c>
-      <c r="F296" s="4" t="n">
+      <c r="F296" s="6" t="n">
         <v>47.62876748023973</v>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -8045,13 +8464,21 @@
       <c r="B297" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C297" s="4" t="n"/>
-      <c r="D297" s="4" t="n"/>
-      <c r="E297" s="4" t="n"/>
-      <c r="F297" s="4" t="n"/>
+      <c r="C297" s="4" t="n">
+        <v>49675</v>
+      </c>
+      <c r="D297" s="4" t="n">
+        <v>27547</v>
+      </c>
+      <c r="E297" s="6" t="n">
+        <v>55.45445395067942</v>
+      </c>
+      <c r="F297" s="6" t="n">
+        <v>44.54554604932058</v>
+      </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -8064,13 +8491,21 @@
       <c r="B298" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C298" s="4" t="n"/>
-      <c r="D298" s="4" t="n"/>
-      <c r="E298" s="4" t="n"/>
-      <c r="F298" s="4" t="n"/>
+      <c r="C298" s="4" t="n">
+        <v>26718</v>
+      </c>
+      <c r="D298" s="4" t="n">
+        <v>14794</v>
+      </c>
+      <c r="E298" s="6" t="n">
+        <v>55.37091099633206</v>
+      </c>
+      <c r="F298" s="6" t="n">
+        <v>44.62908900366794</v>
+      </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -8089,10 +8524,10 @@
       <c r="D299" s="4" t="n">
         <v>6544</v>
       </c>
-      <c r="E299" s="4" t="n">
+      <c r="E299" s="6" t="n">
         <v>48.18851251840942</v>
       </c>
-      <c r="F299" s="4" t="n">
+      <c r="F299" s="6" t="n">
         <v>51.81148748159058</v>
       </c>
       <c r="G299" s="4" t="inlineStr">
@@ -8116,10 +8551,10 @@
       <c r="D300" s="4" t="n">
         <v>5769</v>
       </c>
-      <c r="E300" s="4" t="n">
+      <c r="E300" s="6" t="n">
         <v>49.60020634511221</v>
       </c>
-      <c r="F300" s="4" t="n">
+      <c r="F300" s="6" t="n">
         <v>50.39979365488779</v>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -8143,10 +8578,10 @@
       <c r="D301" s="4" t="n">
         <v>5711</v>
       </c>
-      <c r="E301" s="4" t="n">
+      <c r="E301" s="6" t="n">
         <v>44.95080676898858</v>
       </c>
-      <c r="F301" s="4" t="n">
+      <c r="F301" s="6" t="n">
         <v>55.04919323101142</v>
       </c>
       <c r="G301" s="4" t="inlineStr">
@@ -8170,10 +8605,10 @@
       <c r="D302" s="4" t="n">
         <v>5767</v>
       </c>
-      <c r="E302" s="4" t="n">
+      <c r="E302" s="6" t="n">
         <v>45.56012008216148</v>
       </c>
-      <c r="F302" s="4" t="n">
+      <c r="F302" s="6" t="n">
         <v>54.43987991783852</v>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -8197,10 +8632,10 @@
       <c r="D303" s="4" t="n">
         <v>5128</v>
       </c>
-      <c r="E303" s="4" t="n">
+      <c r="E303" s="6" t="n">
         <v>47.20611249194513</v>
       </c>
-      <c r="F303" s="4" t="n">
+      <c r="F303" s="6" t="n">
         <v>52.79388750805487</v>
       </c>
       <c r="G303" s="4" t="inlineStr">
@@ -8224,10 +8659,10 @@
       <c r="D304" s="4" t="n">
         <v>5800</v>
       </c>
-      <c r="E304" s="4" t="n">
+      <c r="E304" s="6" t="n">
         <v>48.58842255172991</v>
       </c>
-      <c r="F304" s="4" t="n">
+      <c r="F304" s="6" t="n">
         <v>51.41157744827009</v>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -8251,10 +8686,10 @@
       <c r="D305" s="4" t="n">
         <v>6002</v>
       </c>
-      <c r="E305" s="4" t="n">
+      <c r="E305" s="6" t="n">
         <v>43.85503434166301</v>
       </c>
-      <c r="F305" s="4" t="n">
+      <c r="F305" s="6" t="n">
         <v>56.14496565833699</v>
       </c>
       <c r="G305" s="4" t="inlineStr">
@@ -8278,10 +8713,10 @@
       <c r="D306" s="4" t="n">
         <v>6027</v>
       </c>
-      <c r="E306" s="4" t="n">
+      <c r="E306" s="6" t="n">
         <v>43.6897426603842</v>
       </c>
-      <c r="F306" s="4" t="n">
+      <c r="F306" s="6" t="n">
         <v>56.3102573396158</v>
       </c>
       <c r="G306" s="4" t="inlineStr">
@@ -8305,10 +8740,10 @@
       <c r="D307" s="4" t="n">
         <v>6676</v>
       </c>
-      <c r="E307" s="4" t="n">
+      <c r="E307" s="6" t="n">
         <v>48.72281418770982</v>
       </c>
-      <c r="F307" s="4" t="n">
+      <c r="F307" s="6" t="n">
         <v>51.27718581229018</v>
       </c>
       <c r="G307" s="4" t="inlineStr">
@@ -8326,13 +8761,21 @@
       <c r="B308" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C308" s="4" t="n"/>
-      <c r="D308" s="4" t="n"/>
-      <c r="E308" s="4" t="n"/>
-      <c r="F308" s="4" t="n"/>
+      <c r="C308" s="4" t="n">
+        <v>13804</v>
+      </c>
+      <c r="D308" s="4" t="n">
+        <v>6669</v>
+      </c>
+      <c r="E308" s="6" t="n">
+        <v>48.31208345407128</v>
+      </c>
+      <c r="F308" s="6" t="n">
+        <v>51.68791654592872</v>
+      </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -8345,13 +8788,21 @@
       <c r="B309" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C309" s="4" t="n"/>
-      <c r="D309" s="4" t="n"/>
-      <c r="E309" s="4" t="n"/>
-      <c r="F309" s="4" t="n"/>
+      <c r="C309" s="4" t="n">
+        <v>6663</v>
+      </c>
+      <c r="D309" s="4" t="n">
+        <v>3361</v>
+      </c>
+      <c r="E309" s="6" t="n">
+        <v>50.44274350892991</v>
+      </c>
+      <c r="F309" s="6" t="n">
+        <v>49.55725649107009</v>
+      </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -8370,10 +8821,10 @@
       <c r="D310" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E310" s="4" t="n">
+      <c r="E310" s="6" t="n">
         <v>7.142857142857142</v>
       </c>
-      <c r="F310" s="4" t="n">
+      <c r="F310" s="6" t="n">
         <v>92.85714285714286</v>
       </c>
       <c r="G310" s="4" t="inlineStr">
@@ -8397,10 +8848,10 @@
       <c r="D311" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="E311" s="4" t="n">
+      <c r="E311" s="6" t="n">
         <v>11.11111111111111</v>
       </c>
-      <c r="F311" s="4" t="n">
+      <c r="F311" s="6" t="n">
         <v>88.88888888888889</v>
       </c>
       <c r="G311" s="4" t="inlineStr">
@@ -8424,10 +8875,10 @@
       <c r="D312" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E312" s="4" t="n">
+      <c r="E312" s="6" t="n">
         <v>7.480314960629922</v>
       </c>
-      <c r="F312" s="4" t="n">
+      <c r="F312" s="6" t="n">
         <v>92.51968503937007</v>
       </c>
       <c r="G312" s="4" t="inlineStr">
@@ -8451,10 +8902,10 @@
       <c r="D313" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E313" s="4" t="n">
+      <c r="E313" s="6" t="n">
         <v>8.695652173913043</v>
       </c>
-      <c r="F313" s="4" t="n">
+      <c r="F313" s="6" t="n">
         <v>91.30434782608695</v>
       </c>
       <c r="G313" s="4" t="inlineStr">
@@ -8478,10 +8929,10 @@
       <c r="D314" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E314" s="4" t="n">
+      <c r="E314" s="6" t="n">
         <v>9.929078014184398</v>
       </c>
-      <c r="F314" s="4" t="n">
+      <c r="F314" s="6" t="n">
         <v>90.0709219858156</v>
       </c>
       <c r="G314" s="4" t="inlineStr">
@@ -8505,10 +8956,10 @@
       <c r="D315" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="E315" s="4" t="n">
+      <c r="E315" s="6" t="n">
         <v>17.39130434782609</v>
       </c>
-      <c r="F315" s="4" t="n">
+      <c r="F315" s="6" t="n">
         <v>82.60869565217391</v>
       </c>
       <c r="G315" s="4" t="inlineStr">
@@ -8532,10 +8983,10 @@
       <c r="D316" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="E316" s="4" t="n">
+      <c r="E316" s="6" t="n">
         <v>13.47517730496454</v>
       </c>
-      <c r="F316" s="4" t="n">
+      <c r="F316" s="6" t="n">
         <v>86.52482269503545</v>
       </c>
       <c r="G316" s="4" t="inlineStr">
@@ -8559,10 +9010,10 @@
       <c r="D317" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="E317" s="4" t="n">
+      <c r="E317" s="6" t="n">
         <v>16.78321678321678</v>
       </c>
-      <c r="F317" s="4" t="n">
+      <c r="F317" s="6" t="n">
         <v>83.21678321678321</v>
       </c>
       <c r="G317" s="4" t="inlineStr">
@@ -8586,10 +9037,10 @@
       <c r="D318" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="E318" s="4" t="n">
+      <c r="E318" s="6" t="n">
         <v>21.48148148148148</v>
       </c>
-      <c r="F318" s="4" t="n">
+      <c r="F318" s="6" t="n">
         <v>78.51851851851852</v>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -8607,13 +9058,21 @@
       <c r="B319" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C319" s="4" t="n"/>
-      <c r="D319" s="4" t="n"/>
-      <c r="E319" s="4" t="n"/>
-      <c r="F319" s="4" t="n"/>
+      <c r="C319" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="D319" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E319" s="6" t="n">
+        <v>13.8121546961326</v>
+      </c>
+      <c r="F319" s="6" t="n">
+        <v>86.18784530386741</v>
+      </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -8626,13 +9085,21 @@
       <c r="B320" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C320" s="4" t="n"/>
-      <c r="D320" s="4" t="n"/>
-      <c r="E320" s="4" t="n"/>
-      <c r="F320" s="4" t="n"/>
+      <c r="C320" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D320" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E320" s="6" t="n">
+        <v>15.12605042016807</v>
+      </c>
+      <c r="F320" s="6" t="n">
+        <v>84.87394957983193</v>
+      </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -8651,10 +9118,10 @@
       <c r="D321" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="E321" s="4" t="n">
+      <c r="E321" s="6" t="n">
         <v>35.28037383177571</v>
       </c>
-      <c r="F321" s="4" t="n">
+      <c r="F321" s="6" t="n">
         <v>64.71962616822429</v>
       </c>
       <c r="G321" s="4" t="inlineStr">
@@ -8678,10 +9145,10 @@
       <c r="D322" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="E322" s="4" t="n">
+      <c r="E322" s="6" t="n">
         <v>31.28654970760234</v>
       </c>
-      <c r="F322" s="4" t="n">
+      <c r="F322" s="6" t="n">
         <v>68.71345029239765</v>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -8705,10 +9172,10 @@
       <c r="D323" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="E323" s="4" t="n">
+      <c r="E323" s="6" t="n">
         <v>31.0126582278481</v>
       </c>
-      <c r="F323" s="4" t="n">
+      <c r="F323" s="6" t="n">
         <v>68.98734177215189</v>
       </c>
       <c r="G323" s="4" t="inlineStr">
@@ -8732,10 +9199,10 @@
       <c r="D324" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="E324" s="4" t="n">
+      <c r="E324" s="6" t="n">
         <v>34.0983606557377</v>
       </c>
-      <c r="F324" s="4" t="n">
+      <c r="F324" s="6" t="n">
         <v>65.90163934426229</v>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -8759,10 +9226,10 @@
       <c r="D325" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="E325" s="4" t="n">
+      <c r="E325" s="6" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="F325" s="4" t="n">
+      <c r="F325" s="6" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="G325" s="4" t="inlineStr">
@@ -8786,10 +9253,10 @@
       <c r="D326" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="E326" s="4" t="n">
+      <c r="E326" s="6" t="n">
         <v>46.15384615384615</v>
       </c>
-      <c r="F326" s="4" t="n">
+      <c r="F326" s="6" t="n">
         <v>53.84615384615385</v>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -8813,10 +9280,10 @@
       <c r="D327" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="E327" s="4" t="n">
+      <c r="E327" s="6" t="n">
         <v>35.0210970464135</v>
       </c>
-      <c r="F327" s="4" t="n">
+      <c r="F327" s="6" t="n">
         <v>64.9789029535865</v>
       </c>
       <c r="G327" s="4" t="inlineStr">
@@ -8840,10 +9307,10 @@
       <c r="D328" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="E328" s="4" t="n">
+      <c r="E328" s="6" t="n">
         <v>36.81318681318682</v>
       </c>
-      <c r="F328" s="4" t="n">
+      <c r="F328" s="6" t="n">
         <v>63.18681318681318</v>
       </c>
       <c r="G328" s="4" t="inlineStr">
@@ -8867,10 +9334,10 @@
       <c r="D329" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E329" s="4" t="n">
+      <c r="E329" s="6" t="n">
         <v>44.37869822485207</v>
       </c>
-      <c r="F329" s="4" t="n">
+      <c r="F329" s="6" t="n">
         <v>55.62130177514793</v>
       </c>
       <c r="G329" s="4" t="inlineStr">
@@ -8888,13 +9355,21 @@
       <c r="B330" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C330" s="4" t="n"/>
-      <c r="D330" s="4" t="n"/>
-      <c r="E330" s="4" t="n"/>
-      <c r="F330" s="4" t="n"/>
+      <c r="C330" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="D330" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="E330" s="6" t="n">
+        <v>20.42440318302387</v>
+      </c>
+      <c r="F330" s="6" t="n">
+        <v>79.57559681697613</v>
+      </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -8907,13 +9382,21 @@
       <c r="B331" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C331" s="4" t="n"/>
-      <c r="D331" s="4" t="n"/>
-      <c r="E331" s="4" t="n"/>
-      <c r="F331" s="4" t="n"/>
+      <c r="C331" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="D331" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="E331" s="6" t="n">
+        <v>11.5702479338843</v>
+      </c>
+      <c r="F331" s="6" t="n">
+        <v>88.4297520661157</v>
+      </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -8932,10 +9415,10 @@
       <c r="D332" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="E332" s="4" t="n">
+      <c r="E332" s="6" t="n">
         <v>65.71428571428571</v>
       </c>
-      <c r="F332" s="4" t="n">
+      <c r="F332" s="6" t="n">
         <v>34.28571428571429</v>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -8959,10 +9442,10 @@
       <c r="D333" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="E333" s="4" t="n">
+      <c r="E333" s="6" t="n">
         <v>64.17910447761194</v>
       </c>
-      <c r="F333" s="4" t="n">
+      <c r="F333" s="6" t="n">
         <v>35.82089552238806</v>
       </c>
       <c r="G333" s="4" t="inlineStr">
@@ -8986,10 +9469,10 @@
       <c r="D334" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="E334" s="4" t="n">
+      <c r="E334" s="6" t="n">
         <v>67.5</v>
       </c>
-      <c r="F334" s="4" t="n">
+      <c r="F334" s="6" t="n">
         <v>32.5</v>
       </c>
       <c r="G334" s="4" t="inlineStr">
@@ -9013,10 +9496,10 @@
       <c r="D335" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="E335" s="4" t="n">
+      <c r="E335" s="6" t="n">
         <v>72.05882352941177</v>
       </c>
-      <c r="F335" s="4" t="n">
+      <c r="F335" s="6" t="n">
         <v>27.94117647058823</v>
       </c>
       <c r="G335" s="4" t="inlineStr">
@@ -9040,10 +9523,10 @@
       <c r="D336" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="E336" s="4" t="n">
+      <c r="E336" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="F336" s="4" t="n">
+      <c r="F336" s="6" t="n">
         <v>36</v>
       </c>
       <c r="G336" s="4" t="inlineStr">
@@ -9067,10 +9550,10 @@
       <c r="D337" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="E337" s="4" t="n">
+      <c r="E337" s="6" t="n">
         <v>54.28571428571428</v>
       </c>
-      <c r="F337" s="4" t="n">
+      <c r="F337" s="6" t="n">
         <v>45.71428571428572</v>
       </c>
       <c r="G337" s="4" t="inlineStr">
@@ -9094,10 +9577,10 @@
       <c r="D338" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E338" s="4" t="n">
+      <c r="E338" s="6" t="n">
         <v>45.91836734693878</v>
       </c>
-      <c r="F338" s="4" t="n">
+      <c r="F338" s="6" t="n">
         <v>54.08163265306122</v>
       </c>
       <c r="G338" s="4" t="inlineStr">
@@ -9121,10 +9604,10 @@
       <c r="D339" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="E339" s="4" t="n">
+      <c r="E339" s="6" t="n">
         <v>40.65934065934066</v>
       </c>
-      <c r="F339" s="4" t="n">
+      <c r="F339" s="6" t="n">
         <v>59.34065934065934</v>
       </c>
       <c r="G339" s="4" t="inlineStr">
@@ -9148,10 +9631,10 @@
       <c r="D340" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="E340" s="4" t="n">
+      <c r="E340" s="6" t="n">
         <v>62.5</v>
       </c>
-      <c r="F340" s="4" t="n">
+      <c r="F340" s="6" t="n">
         <v>37.5</v>
       </c>
       <c r="G340" s="4" t="inlineStr">
@@ -9169,13 +9652,21 @@
       <c r="B341" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C341" s="4" t="n"/>
-      <c r="D341" s="4" t="n"/>
-      <c r="E341" s="4" t="n"/>
-      <c r="F341" s="4" t="n"/>
+      <c r="C341" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="D341" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="E341" s="6" t="n">
+        <v>69.12751677852349</v>
+      </c>
+      <c r="F341" s="6" t="n">
+        <v>30.87248322147651</v>
+      </c>
       <c r="G341" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -9188,13 +9679,21 @@
       <c r="B342" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C342" s="4" t="n"/>
-      <c r="D342" s="4" t="n"/>
-      <c r="E342" s="4" t="n"/>
-      <c r="F342" s="4" t="n"/>
+      <c r="C342" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="D342" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="E342" s="6" t="n">
+        <v>76.31578947368422</v>
+      </c>
+      <c r="F342" s="6" t="n">
+        <v>23.68421052631578</v>
+      </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -9213,10 +9712,10 @@
       <c r="D343" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="E343" s="4" t="n">
+      <c r="E343" s="6" t="n">
         <v>53.52112676056338</v>
       </c>
-      <c r="F343" s="4" t="n">
+      <c r="F343" s="6" t="n">
         <v>46.47887323943662</v>
       </c>
       <c r="G343" s="4" t="inlineStr">
@@ -9240,10 +9739,10 @@
       <c r="D344" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="E344" s="4" t="n">
+      <c r="E344" s="6" t="n">
         <v>45.56962025316456</v>
       </c>
-      <c r="F344" s="4" t="n">
+      <c r="F344" s="6" t="n">
         <v>54.43037974683544</v>
       </c>
       <c r="G344" s="4" t="inlineStr">
@@ -9267,10 +9766,10 @@
       <c r="D345" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E345" s="4" t="n">
+      <c r="E345" s="6" t="n">
         <v>46.05263157894737</v>
       </c>
-      <c r="F345" s="4" t="n">
+      <c r="F345" s="6" t="n">
         <v>53.94736842105263</v>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -9294,10 +9793,10 @@
       <c r="D346" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="E346" s="4" t="n">
+      <c r="E346" s="6" t="n">
         <v>40.57971014492754</v>
       </c>
-      <c r="F346" s="4" t="n">
+      <c r="F346" s="6" t="n">
         <v>59.42028985507246</v>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -9317,8 +9816,8 @@
       </c>
       <c r="C347" s="4" t="n"/>
       <c r="D347" s="4" t="n"/>
-      <c r="E347" s="4" t="n"/>
-      <c r="F347" s="4" t="n"/>
+      <c r="E347" s="6" t="n"/>
+      <c r="F347" s="6" t="n"/>
       <c r="G347" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -9336,8 +9835,8 @@
       </c>
       <c r="C348" s="4" t="n"/>
       <c r="D348" s="4" t="n"/>
-      <c r="E348" s="4" t="n"/>
-      <c r="F348" s="4" t="n"/>
+      <c r="E348" s="6" t="n"/>
+      <c r="F348" s="6" t="n"/>
       <c r="G348" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -9355,8 +9854,8 @@
       </c>
       <c r="C349" s="4" t="n"/>
       <c r="D349" s="4" t="n"/>
-      <c r="E349" s="4" t="n"/>
-      <c r="F349" s="4" t="n"/>
+      <c r="E349" s="6" t="n"/>
+      <c r="F349" s="6" t="n"/>
       <c r="G349" s="4" t="inlineStr">
         <is>
           <t>Combined into Dadra &amp; Nagar Haveli</t>
@@ -9374,8 +9873,8 @@
       </c>
       <c r="C350" s="4" t="n"/>
       <c r="D350" s="4" t="n"/>
-      <c r="E350" s="4" t="n"/>
-      <c r="F350" s="4" t="n"/>
+      <c r="E350" s="6" t="n"/>
+      <c r="F350" s="6" t="n"/>
       <c r="G350" s="4" t="inlineStr">
         <is>
           <t>Combined into Dadra &amp; Nagar Haveli</t>
@@ -9393,8 +9892,8 @@
       </c>
       <c r="C351" s="4" t="n"/>
       <c r="D351" s="4" t="n"/>
-      <c r="E351" s="4" t="n"/>
-      <c r="F351" s="4" t="n"/>
+      <c r="E351" s="6" t="n"/>
+      <c r="F351" s="6" t="n"/>
       <c r="G351" s="4" t="inlineStr">
         <is>
           <t>Combined into Dadra &amp; Nagar Haveli</t>
@@ -9412,11 +9911,11 @@
       </c>
       <c r="C352" s="4" t="n"/>
       <c r="D352" s="4" t="n"/>
-      <c r="E352" s="4" t="n"/>
-      <c r="F352" s="4" t="n"/>
+      <c r="E352" s="6" t="n"/>
+      <c r="F352" s="6" t="n"/>
       <c r="G352" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>NA — separate Daman &amp; Diu value not reported in supplied 2025/2026 table</t>
         </is>
       </c>
     </row>
@@ -9431,11 +9930,11 @@
       </c>
       <c r="C353" s="4" t="n"/>
       <c r="D353" s="4" t="n"/>
-      <c r="E353" s="4" t="n"/>
-      <c r="F353" s="4" t="n"/>
+      <c r="E353" s="6" t="n"/>
+      <c r="F353" s="6" t="n"/>
       <c r="G353" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>NA — separate Daman &amp; Diu value not reported in supplied 2025/2026 table</t>
         </is>
       </c>
     </row>
@@ -9454,10 +9953,10 @@
       <c r="D354" s="4" t="n">
         <v>1591</v>
       </c>
-      <c r="E354" s="4" t="n">
+      <c r="E354" s="6" t="n">
         <v>21.5728813559322</v>
       </c>
-      <c r="F354" s="4" t="n">
+      <c r="F354" s="6" t="n">
         <v>78.4271186440678</v>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -9481,10 +9980,10 @@
       <c r="D355" s="4" t="n">
         <v>1584</v>
       </c>
-      <c r="E355" s="4" t="n">
+      <c r="E355" s="6" t="n">
         <v>23.7374494230481</v>
       </c>
-      <c r="F355" s="4" t="n">
+      <c r="F355" s="6" t="n">
         <v>76.2625505769519</v>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -9508,10 +10007,10 @@
       <c r="D356" s="4" t="n">
         <v>1690</v>
       </c>
-      <c r="E356" s="4" t="n">
+      <c r="E356" s="6" t="n">
         <v>25.9401381427475</v>
       </c>
-      <c r="F356" s="4" t="n">
+      <c r="F356" s="6" t="n">
         <v>74.0598618572525</v>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -9535,10 +10034,10 @@
       <c r="D357" s="4" t="n">
         <v>1463</v>
       </c>
-      <c r="E357" s="4" t="n">
+      <c r="E357" s="6" t="n">
         <v>26.07843137254902</v>
       </c>
-      <c r="F357" s="4" t="n">
+      <c r="F357" s="6" t="n">
         <v>73.92156862745098</v>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -9562,10 +10061,10 @@
       <c r="D358" s="4" t="n">
         <v>1196</v>
       </c>
-      <c r="E358" s="4" t="n">
+      <c r="E358" s="6" t="n">
         <v>28.6261369076113</v>
       </c>
-      <c r="F358" s="4" t="n">
+      <c r="F358" s="6" t="n">
         <v>71.3738630923887</v>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -9589,10 +10088,10 @@
       <c r="D359" s="4" t="n">
         <v>1239</v>
       </c>
-      <c r="E359" s="4" t="n">
+      <c r="E359" s="6" t="n">
         <v>26.25</v>
       </c>
-      <c r="F359" s="4" t="n">
+      <c r="F359" s="6" t="n">
         <v>73.75</v>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -9616,10 +10115,10 @@
       <c r="D360" s="4" t="n">
         <v>1461</v>
       </c>
-      <c r="E360" s="4" t="n">
+      <c r="E360" s="6" t="n">
         <v>25.84925690021231</v>
       </c>
-      <c r="F360" s="4" t="n">
+      <c r="F360" s="6" t="n">
         <v>74.15074309978769</v>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -9643,10 +10142,10 @@
       <c r="D361" s="4" t="n">
         <v>1457</v>
       </c>
-      <c r="E361" s="4" t="n">
+      <c r="E361" s="6" t="n">
         <v>24.9742886527254</v>
       </c>
-      <c r="F361" s="4" t="n">
+      <c r="F361" s="6" t="n">
         <v>75.02571134727459</v>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -9670,10 +10169,10 @@
       <c r="D362" s="4" t="n">
         <v>1551</v>
       </c>
-      <c r="E362" s="4" t="n">
+      <c r="E362" s="6" t="n">
         <v>27.41735902421778</v>
       </c>
-      <c r="F362" s="4" t="n">
+      <c r="F362" s="6" t="n">
         <v>72.58264097578221</v>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -9691,13 +10190,21 @@
       <c r="B363" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C363" s="4" t="n"/>
-      <c r="D363" s="4" t="n"/>
-      <c r="E363" s="4" t="n"/>
-      <c r="F363" s="4" t="n"/>
+      <c r="C363" s="4" t="n">
+        <v>5994</v>
+      </c>
+      <c r="D363" s="4" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E363" s="6" t="n">
+        <v>24.40774107440774</v>
+      </c>
+      <c r="F363" s="6" t="n">
+        <v>75.59225892559226</v>
+      </c>
       <c r="G363" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -9710,13 +10217,21 @@
       <c r="B364" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C364" s="4" t="n"/>
-      <c r="D364" s="4" t="n"/>
-      <c r="E364" s="4" t="n"/>
-      <c r="F364" s="4" t="n"/>
+      <c r="C364" s="4" t="n">
+        <v>6875</v>
+      </c>
+      <c r="D364" s="4" t="n">
+        <v>810</v>
+      </c>
+      <c r="E364" s="6" t="n">
+        <v>11.78181818181818</v>
+      </c>
+      <c r="F364" s="6" t="n">
+        <v>88.21818181818182</v>
+      </c>
       <c r="G364" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -9735,10 +10250,10 @@
       <c r="D365" s="4" t="n">
         <v>958</v>
       </c>
-      <c r="E365" s="4" t="n">
+      <c r="E365" s="6" t="n">
         <v>17.41501545173605</v>
       </c>
-      <c r="F365" s="4" t="n">
+      <c r="F365" s="6" t="n">
         <v>82.58498454826395</v>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -9762,10 +10277,10 @@
       <c r="D366" s="4" t="n">
         <v>926</v>
       </c>
-      <c r="E366" s="4" t="n">
+      <c r="E366" s="6" t="n">
         <v>16.4651493598862</v>
       </c>
-      <c r="F366" s="4" t="n">
+      <c r="F366" s="6" t="n">
         <v>83.5348506401138</v>
       </c>
       <c r="G366" s="4" t="inlineStr">
@@ -9789,10 +10304,10 @@
       <c r="D367" s="4" t="n">
         <v>984</v>
       </c>
-      <c r="E367" s="4" t="n">
+      <c r="E367" s="6" t="n">
         <v>16.46035463365674</v>
       </c>
-      <c r="F367" s="4" t="n">
+      <c r="F367" s="6" t="n">
         <v>83.53964536634325</v>
       </c>
       <c r="G367" s="4" t="inlineStr">
@@ -9816,10 +10331,10 @@
       <c r="D368" s="4" t="n">
         <v>996</v>
       </c>
-      <c r="E368" s="4" t="n">
+      <c r="E368" s="6" t="n">
         <v>17.18426501035197</v>
       </c>
-      <c r="F368" s="4" t="n">
+      <c r="F368" s="6" t="n">
         <v>82.81573498964804</v>
       </c>
       <c r="G368" s="4" t="inlineStr">
@@ -9843,10 +10358,10 @@
       <c r="D369" s="4" t="n">
         <v>728</v>
       </c>
-      <c r="E369" s="4" t="n">
+      <c r="E369" s="6" t="n">
         <v>14.97942386831276</v>
       </c>
-      <c r="F369" s="4" t="n">
+      <c r="F369" s="6" t="n">
         <v>85.02057613168725</v>
       </c>
       <c r="G369" s="4" t="inlineStr">
@@ -9870,10 +10385,10 @@
       <c r="D370" s="4" t="n">
         <v>774</v>
       </c>
-      <c r="E370" s="4" t="n">
+      <c r="E370" s="6" t="n">
         <v>14.19662509170946</v>
       </c>
-      <c r="F370" s="4" t="n">
+      <c r="F370" s="6" t="n">
         <v>85.80337490829054</v>
       </c>
       <c r="G370" s="4" t="inlineStr">
@@ -9897,10 +10412,10 @@
       <c r="D371" s="4" t="n">
         <v>805</v>
       </c>
-      <c r="E371" s="4" t="n">
+      <c r="E371" s="6" t="n">
         <v>13.21405121470781</v>
       </c>
-      <c r="F371" s="4" t="n">
+      <c r="F371" s="6" t="n">
         <v>86.78594878529219</v>
       </c>
       <c r="G371" s="4" t="inlineStr">
@@ -9924,10 +10439,10 @@
       <c r="D372" s="4" t="n">
         <v>893</v>
       </c>
-      <c r="E372" s="4" t="n">
+      <c r="E372" s="6" t="n">
         <v>14.17910447761194</v>
       </c>
-      <c r="F372" s="4" t="n">
+      <c r="F372" s="6" t="n">
         <v>85.82089552238806</v>
       </c>
       <c r="G372" s="4" t="inlineStr">
@@ -9951,10 +10466,10 @@
       <c r="D373" s="4" t="n">
         <v>831</v>
       </c>
-      <c r="E373" s="4" t="n">
+      <c r="E373" s="6" t="n">
         <v>14.30785123966942</v>
       </c>
-      <c r="F373" s="4" t="n">
+      <c r="F373" s="6" t="n">
         <v>85.69214876033058</v>
       </c>
       <c r="G373" s="4" t="inlineStr">
@@ -9972,13 +10487,21 @@
       <c r="B374" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C374" s="4" t="n"/>
-      <c r="D374" s="4" t="n"/>
-      <c r="E374" s="4" t="n"/>
-      <c r="F374" s="4" t="n"/>
+      <c r="C374" s="4" t="n">
+        <v>5318</v>
+      </c>
+      <c r="D374" s="4" t="n">
+        <v>984</v>
+      </c>
+      <c r="E374" s="6" t="n">
+        <v>18.50319669048514</v>
+      </c>
+      <c r="F374" s="6" t="n">
+        <v>81.49680330951486</v>
+      </c>
       <c r="G374" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -9991,13 +10514,21 @@
       <c r="B375" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C375" s="4" t="n"/>
-      <c r="D375" s="4" t="n"/>
-      <c r="E375" s="4" t="n"/>
-      <c r="F375" s="4" t="n"/>
+      <c r="C375" s="4" t="n">
+        <v>3269</v>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>603</v>
+      </c>
+      <c r="E375" s="6" t="n">
+        <v>18.4460079535026</v>
+      </c>
+      <c r="F375" s="6" t="n">
+        <v>81.5539920464974</v>
+      </c>
       <c r="G375" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -10012,8 +10543,8 @@
       </c>
       <c r="C376" s="4" t="n"/>
       <c r="D376" s="4" t="n"/>
-      <c r="E376" s="4" t="n"/>
-      <c r="F376" s="4" t="n"/>
+      <c r="E376" s="6" t="n"/>
+      <c r="F376" s="6" t="n"/>
       <c r="G376" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -10031,8 +10562,8 @@
       </c>
       <c r="C377" s="4" t="n"/>
       <c r="D377" s="4" t="n"/>
-      <c r="E377" s="4" t="n"/>
-      <c r="F377" s="4" t="n"/>
+      <c r="E377" s="6" t="n"/>
+      <c r="F377" s="6" t="n"/>
       <c r="G377" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -10050,8 +10581,8 @@
       </c>
       <c r="C378" s="4" t="n"/>
       <c r="D378" s="4" t="n"/>
-      <c r="E378" s="4" t="n"/>
-      <c r="F378" s="4" t="n"/>
+      <c r="E378" s="6" t="n"/>
+      <c r="F378" s="6" t="n"/>
       <c r="G378" s="4" t="inlineStr">
         <is>
           <t>Official MoRTH/PIB state table (2024 cross-check)</t>
@@ -10069,8 +10600,8 @@
       </c>
       <c r="C379" s="4" t="n"/>
       <c r="D379" s="4" t="n"/>
-      <c r="E379" s="4" t="n"/>
-      <c r="F379" s="4" t="n"/>
+      <c r="E379" s="6" t="n"/>
+      <c r="F379" s="6" t="n"/>
       <c r="G379" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -10088,8 +10619,8 @@
       </c>
       <c r="C380" s="4" t="n"/>
       <c r="D380" s="4" t="n"/>
-      <c r="E380" s="4" t="n"/>
-      <c r="F380" s="4" t="n"/>
+      <c r="E380" s="6" t="n"/>
+      <c r="F380" s="6" t="n"/>
       <c r="G380" s="4" t="inlineStr">
         <is>
           <t>Not available in current state series</t>
@@ -10111,10 +10642,10 @@
       <c r="D381" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="E381" s="4" t="n">
+      <c r="E381" s="6" t="n">
         <v>23.72881355932203</v>
       </c>
-      <c r="F381" s="4" t="n">
+      <c r="F381" s="6" t="n">
         <v>76.27118644067797</v>
       </c>
       <c r="G381" s="4" t="inlineStr">
@@ -10138,10 +10669,10 @@
       <c r="D382" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="E382" s="4" t="n">
+      <c r="E382" s="6" t="n">
         <v>16.57754010695187</v>
       </c>
-      <c r="F382" s="4" t="n">
+      <c r="F382" s="6" t="n">
         <v>83.42245989304813</v>
       </c>
       <c r="G382" s="4" t="inlineStr">
@@ -10165,10 +10696,10 @@
       <c r="D383" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="E383" s="4" t="n">
+      <c r="E383" s="6" t="n">
         <v>20.41522491349481</v>
       </c>
-      <c r="F383" s="4" t="n">
+      <c r="F383" s="6" t="n">
         <v>79.58477508650519</v>
       </c>
       <c r="G383" s="4" t="inlineStr">
@@ -10192,10 +10723,10 @@
       <c r="D384" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="E384" s="4" t="n">
+      <c r="E384" s="6" t="n">
         <v>23.10606060606061</v>
       </c>
-      <c r="F384" s="4" t="n">
+      <c r="F384" s="6" t="n">
         <v>76.89393939393939</v>
       </c>
       <c r="G384" s="4" t="inlineStr">
@@ -10213,13 +10744,21 @@
       <c r="B385" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C385" s="4" t="n"/>
-      <c r="D385" s="4" t="n"/>
-      <c r="E385" s="4" t="n"/>
-      <c r="F385" s="4" t="n"/>
+      <c r="C385" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="D385" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E385" s="6" t="n">
+        <v>24.73867595818815</v>
+      </c>
+      <c r="F385" s="6" t="n">
+        <v>75.26132404181185</v>
+      </c>
       <c r="G385" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -10232,13 +10771,21 @@
       <c r="B386" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C386" s="4" t="n"/>
-      <c r="D386" s="4" t="n"/>
-      <c r="E386" s="4" t="n"/>
-      <c r="F386" s="4" t="n"/>
+      <c r="C386" s="4" t="n">
+        <v>235</v>
+      </c>
+      <c r="D386" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E386" s="6" t="n">
+        <v>16.59574468085106</v>
+      </c>
+      <c r="F386" s="6" t="n">
+        <v>83.40425531914894</v>
+      </c>
       <c r="G386" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -10257,10 +10804,10 @@
       <c r="D387" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E387" s="4" t="n">
+      <c r="E387" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="F387" s="4" t="n">
+      <c r="F387" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G387" s="4" t="inlineStr">
@@ -10284,10 +10831,10 @@
       <c r="D388" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E388" s="4" t="n">
+      <c r="E388" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F388" s="4" t="n">
+      <c r="F388" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G388" s="4" t="inlineStr">
@@ -10311,10 +10858,10 @@
       <c r="D389" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E389" s="4" t="n">
+      <c r="E389" s="6" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="F389" s="4" t="n">
+      <c r="F389" s="6" t="n">
         <v>66.66666666666667</v>
       </c>
       <c r="G389" s="4" t="inlineStr">
@@ -10338,10 +10885,10 @@
       <c r="D390" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E390" s="4" t="n">
+      <c r="E390" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F390" s="4" t="n">
+      <c r="F390" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G390" s="4" t="inlineStr">
@@ -10365,10 +10912,10 @@
       <c r="D391" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E391" s="4" t="n">
+      <c r="E391" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F391" s="4" t="n">
+      <c r="F391" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G391" s="4" t="inlineStr">
@@ -10392,10 +10939,10 @@
       <c r="D392" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E392" s="4" t="n">
+      <c r="E392" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F392" s="4" t="n">
+      <c r="F392" s="6" t="n">
         <v>75</v>
       </c>
       <c r="G392" s="4" t="inlineStr">
@@ -10419,10 +10966,10 @@
       <c r="D393" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E393" s="4" t="n">
+      <c r="E393" s="6" t="n">
         <v>66.66666666666666</v>
       </c>
-      <c r="F393" s="4" t="n">
+      <c r="F393" s="6" t="n">
         <v>33.33333333333334</v>
       </c>
       <c r="G393" s="4" t="inlineStr">
@@ -10446,10 +10993,10 @@
       <c r="D394" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E394" s="4" t="n">
+      <c r="E394" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F394" s="4" t="n">
+      <c r="F394" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G394" s="4" t="inlineStr">
@@ -10473,8 +11020,8 @@
       <c r="D395" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E395" s="4" t="n"/>
-      <c r="F395" s="4" t="n"/>
+      <c r="E395" s="6" t="n"/>
+      <c r="F395" s="6" t="n"/>
       <c r="G395" s="4" t="inlineStr">
         <is>
           <t>Official Government / Rajya Sabha 18-Mar-2026</t>
@@ -10490,13 +11037,21 @@
       <c r="B396" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C396" s="4" t="n"/>
-      <c r="D396" s="4" t="n"/>
-      <c r="E396" s="4" t="n"/>
-      <c r="F396" s="4" t="n"/>
+      <c r="C396" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D396" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F396" s="6" t="n">
+        <v>100</v>
+      </c>
       <c r="G396" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -10509,13 +11064,17 @@
       <c r="B397" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C397" s="4" t="n"/>
-      <c r="D397" s="4" t="n"/>
-      <c r="E397" s="4" t="n"/>
-      <c r="F397" s="4" t="n"/>
+      <c r="C397" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" s="6" t="n"/>
+      <c r="F397" s="6" t="n"/>
       <c r="G397" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -10534,10 +11093,10 @@
       <c r="D398" s="4" t="n">
         <v>244</v>
       </c>
-      <c r="E398" s="4" t="n">
+      <c r="E398" s="6" t="n">
         <v>13.81653454133635</v>
       </c>
-      <c r="F398" s="4" t="n">
+      <c r="F398" s="6" t="n">
         <v>86.18346545866365</v>
       </c>
       <c r="G398" s="4" t="inlineStr">
@@ -10561,10 +11120,10 @@
       <c r="D399" s="4" t="n">
         <v>233</v>
       </c>
-      <c r="E399" s="4" t="n">
+      <c r="E399" s="6" t="n">
         <v>13.76255168340224</v>
       </c>
-      <c r="F399" s="4" t="n">
+      <c r="F399" s="6" t="n">
         <v>86.23744831659775</v>
       </c>
       <c r="G399" s="4" t="inlineStr">
@@ -10588,10 +11147,10 @@
       <c r="D400" s="4" t="n">
         <v>226</v>
       </c>
-      <c r="E400" s="4" t="n">
+      <c r="E400" s="6" t="n">
         <v>14.15153412648716</v>
       </c>
-      <c r="F400" s="4" t="n">
+      <c r="F400" s="6" t="n">
         <v>85.84846587351284</v>
       </c>
       <c r="G400" s="4" t="inlineStr">
@@ -10615,10 +11174,10 @@
       <c r="D401" s="4" t="n">
         <v>147</v>
       </c>
-      <c r="E401" s="4" t="n">
+      <c r="E401" s="6" t="n">
         <v>10.56034482758621</v>
       </c>
-      <c r="F401" s="4" t="n">
+      <c r="F401" s="6" t="n">
         <v>89.43965517241379</v>
       </c>
       <c r="G401" s="4" t="inlineStr">
@@ -10642,10 +11201,10 @@
       <c r="D402" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="E402" s="4" t="n">
+      <c r="E402" s="6" t="n">
         <v>14.96388028895769</v>
       </c>
-      <c r="F402" s="4" t="n">
+      <c r="F402" s="6" t="n">
         <v>85.03611971104232</v>
       </c>
       <c r="G402" s="4" t="inlineStr">
@@ -10669,10 +11228,10 @@
       <c r="D403" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="E403" s="4" t="n">
+      <c r="E403" s="6" t="n">
         <v>13.34604385128694</v>
       </c>
-      <c r="F403" s="4" t="n">
+      <c r="F403" s="6" t="n">
         <v>86.65395614871306</v>
       </c>
       <c r="G403" s="4" t="inlineStr">
@@ -10696,10 +11255,10 @@
       <c r="D404" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="E404" s="4" t="n">
+      <c r="E404" s="6" t="n">
         <v>15.3259949195597</v>
       </c>
-      <c r="F404" s="4" t="n">
+      <c r="F404" s="6" t="n">
         <v>84.67400508044031</v>
       </c>
       <c r="G404" s="4" t="inlineStr">
@@ -10723,10 +11282,10 @@
       <c r="D405" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="E405" s="4" t="n">
+      <c r="E405" s="6" t="n">
         <v>11.3914373088685</v>
       </c>
-      <c r="F405" s="4" t="n">
+      <c r="F405" s="6" t="n">
         <v>88.6085626911315</v>
       </c>
       <c r="G405" s="4" t="inlineStr">
@@ -10750,10 +11309,10 @@
       <c r="D406" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="E406" s="4" t="n">
+      <c r="E406" s="6" t="n">
         <v>15.23410202655486</v>
       </c>
-      <c r="F406" s="4" t="n">
+      <c r="F406" s="6" t="n">
         <v>84.76589797344513</v>
       </c>
       <c r="G406" s="4" t="inlineStr">
@@ -10771,13 +11330,21 @@
       <c r="B407" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C407" s="4" t="n"/>
-      <c r="D407" s="4" t="n"/>
-      <c r="E407" s="4" t="n"/>
-      <c r="F407" s="4" t="n"/>
+      <c r="C407" s="4" t="n">
+        <v>1689</v>
+      </c>
+      <c r="D407" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="E407" s="6" t="n">
+        <v>14.2687981053878</v>
+      </c>
+      <c r="F407" s="6" t="n">
+        <v>85.7312018946122</v>
+      </c>
       <c r="G407" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Official state/UT table</t>
         </is>
       </c>
     </row>
@@ -10790,13 +11357,21 @@
       <c r="B408" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C408" s="4" t="n"/>
-      <c r="D408" s="4" t="n"/>
-      <c r="E408" s="4" t="n"/>
-      <c r="F408" s="4" t="n"/>
+      <c r="C408" s="4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D408" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="E408" s="6" t="n">
+        <v>10.95100864553314</v>
+      </c>
+      <c r="F408" s="6" t="n">
+        <v>89.04899135446686</v>
+      </c>
       <c r="G408" s="4" t="inlineStr">
         <is>
-          <t>Not available in current state series</t>
+          <t>Provisional e-DAR through 27 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -10991,10 +11566,10 @@
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>513563</v>
+        <v>513474</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>183382</v>
+        <v>183434</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -11029,7 +11604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11044,7 +11619,7 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>2016–2026 dashboard-compatible dataset. 2025 is the latest full-year national figure in the current series; 2026 is provisional/YTD and is not a full calendar year.</t>
+          <t>2016–2026 dashboard-compatible dataset. 2025 is full-year and 2026 is provisional/YTD through 27 July 2026.</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11691,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>State-wise series intentionally not populated. 2025 is national full-year only; 2026 is provisional/YTD through 27-Jul-2026.</t>
+          <t>2025 full-year and 2026 provisional/YTD state-wise values are populated from the supplied Ministry of Road Transport &amp; Highways / Government of India parliamentary annexure. 2026 covers 1 January–27 July 2026.</t>
         </is>
       </c>
     </row>
@@ -11153,6 +11728,18 @@
       <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Completed: corrected 2018 state accident values; corrected 2022–2024 state accidents/fatalities; recomputed all affected rates/survival values; verified annual state sums against official totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025–2026 source</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supplied workbook: India_All_State_UT_Road_Accidents_2025_to_27_July_2026.xlsx; source cited there as Lok Sabha Unstarred Question No. 1939, answered 30 July 2026, Annexure-I.</t>
         </is>
       </c>
     </row>
